--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,358 +42,358 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
     <x:t>RJC VICTORY FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
   </x:si>
   <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOSS, JEREMY</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAMPA-NAJJAR, AMMAR</x:t>
   </x:si>
   <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLLINS, KINA</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
     <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
     <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -882,7 +882,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>362844</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -890,117 +890,117 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>3515615</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>-62727</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>11995</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>10000</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>382</x:v>
+        <x:v>685625</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -1011,16 +1011,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>500000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1028,183 +1028,183 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>333</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>333</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>715</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>382</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>382</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>382</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>382</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1212,114 +1212,114 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>14264</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1327,45 +1327,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>382</x:v>
+        <x:v>-22643</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>2000000</x:v>
+        <x:v>8437450</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1373,48 +1373,48 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>382</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>1974</x:v>
+        <x:v>80291</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
@@ -1425,131 +1425,131 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2538</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>2649</x:v>
+        <x:v>2457788</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2651</x:v>
+        <x:v>2061287</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>938</x:v>
+        <x:v>1137283</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-9678</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>-31053</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1557,22 +1557,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>3575107</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1580,45 +1580,45 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="D33" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F33" s="1">
-        <x:v>4968501</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>-6917</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1626,22 +1626,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-46</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1649,22 +1649,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F36" s="1">
-        <x:v>59748</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1672,68 +1672,68 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>579319</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>5734013</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1741,459 +1741,459 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-28160</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-22643</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>2346358</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>8437450</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>39386</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>149773</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>60000</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>63298</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>152765</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>500346</x:v>
+        <x:v>2538</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>198972</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C51" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>198972</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>600000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>80291</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>253656</x:v>
+        <x:v>31115</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="C55" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>350000</x:v>
+        <x:v>50000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>499160</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>214831</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>4379243</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>663879</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2201,22 +2201,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2224,91 +2224,91 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>104555</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>3985698</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>4383748</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>1426379</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2316,22 +2316,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>1642139</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2339,229 +2339,229 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>108000</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>663879</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>685625</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>825294</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1183678</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>4383749</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>1426379</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2569,114 +2569,114 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>104555</x:v>
+        <x:v>2346358</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>3515616</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1137283</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>2457788</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2684,117 +2684,117 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>253750</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>50000</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F83" s="1">
         <x:v>17793547</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>31115</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>2061287</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2843,1005 +2843,1005 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>8758871</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>4968501</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>7971780</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>209110</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>149773</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>9267843</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7610550</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>5734395</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>50000</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>10542390</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>2649</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2435145</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>685625</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>2651</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>938</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>1974</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1217574</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C44" s="1" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>253656</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>408441</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>11995</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>39386</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>164138</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>-62727</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>214831</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3886,730 +3886,730 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>8758871</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>4968501</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>7971780</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>9626726</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7610550</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>5734395</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>10592390</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2649</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2435145</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>685625</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>2651</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>600000</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>938</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>1219930</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>253656</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>408441</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>11995</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>39386</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>164138</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>-62727</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>214831</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4650,321 +4650,321 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>31325878</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7610550</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>5734395</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>10592772</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>2649</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2435145</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>685625</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>602651</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>198972</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1220868</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>662097</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>12377</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>764</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>203524</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>-62727</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>214831</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>382</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5001,7 +5001,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5009,7 +5009,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -5017,7 +5017,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5025,7 +5025,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>37923820</x:v>
@@ -5033,7 +5033,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-6917</x:v>
@@ -5041,7 +5041,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14781122</x:v>
@@ -5049,7 +5049,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>5734395</x:v>
@@ -5057,7 +5057,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>30732677</x:v>
@@ -5065,7 +5065,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>2649</x:v>
@@ -5073,7 +5073,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3120770</x:v>
@@ -5081,7 +5081,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>602651</x:v>
@@ -5089,7 +5089,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>399814</x:v>
@@ -5097,7 +5097,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1220868</x:v>
@@ -5105,7 +5105,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>5315931</x:v>
@@ -5113,7 +5113,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>-18676</x:v>
@@ -5121,7 +5121,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>764</x:v>
@@ -5129,7 +5129,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>217742</x:v>
@@ -5137,7 +5137,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>-62727</x:v>
@@ -5145,7 +5145,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>214831</x:v>
@@ -5153,7 +5153,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -5197,10 +5197,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5208,10 +5208,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5219,10 +5219,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5230,10 +5230,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5241,10 +5241,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5252,10 +5252,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5263,10 +5263,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5274,10 +5274,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>8758489</x:v>
@@ -5285,10 +5285,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3904224</x:v>
@@ -5296,10 +5296,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>764</x:v>
@@ -5307,10 +5307,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>500346</x:v>
@@ -5318,10 +5318,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>19591653</x:v>
@@ -5329,10 +5329,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>149773</x:v>
@@ -5340,10 +5340,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>5018571</x:v>
@@ -5351,10 +5351,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>-6917</x:v>
@@ -5362,10 +5362,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>10626696</x:v>
@@ -5373,10 +5373,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4154426</x:v>
@@ -5384,10 +5384,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>382</x:v>
@@ -5395,10 +5395,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5734013</x:v>
@@ -5406,10 +5406,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>34035</x:v>
@@ -5417,10 +5417,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>50000</x:v>
@@ -5428,10 +5428,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>10000</x:v>
@@ -5439,10 +5439,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>30638642</x:v>
@@ -5450,10 +5450,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>2649</x:v>
@@ -5461,10 +5461,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3120770</x:v>
@@ -5472,10 +5472,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>600000</x:v>
@@ -5483,10 +5483,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2651</x:v>
@@ -5494,10 +5494,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1870</x:v>
@@ -5505,10 +5505,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>397944</x:v>
@@ -5516,10 +5516,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1217574</x:v>
@@ -5527,10 +5527,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>3294</x:v>
@@ -5538,10 +5538,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>603656</x:v>
@@ -5549,10 +5549,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>58441</x:v>
@@ -5560,10 +5560,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>4653834</x:v>
@@ -5571,10 +5571,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>382</x:v>
@@ -5582,10 +5582,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>11995</x:v>
@@ -5593,10 +5593,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>-31053</x:v>
@@ -5604,10 +5604,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>764</x:v>
@@ -5615,10 +5615,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>178402</x:v>
@@ -5626,10 +5626,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>39386</x:v>
@@ -5637,10 +5637,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>-46</x:v>
@@ -5648,10 +5648,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-62727</x:v>
@@ -5659,10 +5659,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>214831</x:v>
@@ -5670,10 +5670,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -81,6 +81,21 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -90,9 +105,6 @@
     <x:t>MCADAMS, BEN</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>UT</x:t>
   </x:si>
   <x:si>
@@ -108,18 +120,6 @@
     <x:t>09</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -165,30 +165,219 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>STELSON, JANELLE</x:t>
   </x:si>
   <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONLEY, CAIT</x:t>
   </x:si>
   <x:si>
@@ -198,202 +387,13 @@
     <x:t>GALINDO, MAUREEN</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>SULLIVAN, MAURA CORBY</x:t>
   </x:si>
   <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUSH, CORI</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -464,8 +464,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G85" totalsRowShown="0">
-  <x:autoFilter ref="A1:G85"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
+  <x:autoFilter ref="A1:G81"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -829,7 +829,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G85"/>
+  <x:dimension ref="A1:G81"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -951,7 +951,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>214831</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -968,13 +968,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>4383748</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -991,13 +991,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>685625</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1005,16 +1005,16 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>17</x:v>
@@ -1120,10 +1120,10 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>46</x:v>
@@ -1143,10 +1143,10 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>35</x:v>
@@ -1198,16 +1198,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>382</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
@@ -1218,13 +1218,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F17" s="1">
         <x:v>382</x:v>
@@ -1241,19 +1241,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
@@ -1270,56 +1270,56 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>382</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>14264</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>382</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1327,45 +1327,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>-22643</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>8437450</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1373,22 +1373,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>500346</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1396,25 +1396,25 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>80291</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
@@ -1425,85 +1425,85 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>1426379</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>2457788</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2061287</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>1137283</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1511,25 +1511,25 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
@@ -1540,13 +1540,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F31" s="1">
         <x:v>715</x:v>
@@ -1563,13 +1563,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F32" s="1">
         <x:v>938</x:v>
@@ -1580,19 +1580,19 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F33" s="1">
         <x:v>63298</x:v>
@@ -1603,19 +1603,19 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F34" s="1">
         <x:v>600000</x:v>
@@ -1626,10 +1626,10 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
         <x:v>15</x:v>
@@ -1649,19 +1649,19 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F36" s="1">
         <x:v>825294</x:v>
@@ -1672,10 +1672,10 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>15</x:v>
@@ -1695,25 +1695,25 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>333</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1724,16 +1724,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>1974</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1741,71 +1741,71 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-46</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>2326917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
@@ -1816,16 +1816,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>499160</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1833,71 +1833,71 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>663879</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>1642139</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
@@ -1908,62 +1908,62 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>-62727</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>382</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>2538</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1977,16 +1977,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>2651</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -1994,114 +1994,114 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-6917</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>149773</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>104555</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>31115</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>50000</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2109,91 +2109,91 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>253750</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>104555</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>362844</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>333</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2207,13 +2207,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F60" s="1">
         <x:v>382</x:v>
@@ -2224,91 +2224,91 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>3575107</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>59748</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-28160</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>39386</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2322,16 +2322,16 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>198972</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2339,22 +2339,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="C66" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>4379243</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2362,68 +2362,68 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>3232621</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>2326917</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -2437,19 +2437,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>500000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
@@ -2460,16 +2460,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>382</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2483,19 +2483,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
@@ -2506,76 +2506,76 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>2000000</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>-9678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>5734013</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
         <x:v>10</x:v>
@@ -2584,30 +2584,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2346358</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>60000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2615,22 +2615,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>152765</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2638,45 +2638,45 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>198972</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>253656</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2684,117 +2684,25 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>350000</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:7">
-      <x:c r="A82" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B82" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C82" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D82" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E82" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F82" s="1">
-        <x:v>1183678</x:v>
-      </x:c>
-      <x:c r="G82" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:7">
-      <x:c r="A83" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B83" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C83" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F83" s="1">
-        <x:v>17793547</x:v>
-      </x:c>
-      <x:c r="G83" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:7">
-      <x:c r="A84" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="B84" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C84" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="E84" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F84" s="1">
-        <x:v>108000</x:v>
-      </x:c>
-      <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:7">
-      <x:c r="A85" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="B85" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C85" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="D85" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E85" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F85" s="1">
-        <x:v>1183678</x:v>
-      </x:c>
-      <x:c r="G85" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2843,13 +2751,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2860,13 +2768,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2877,13 +2785,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2894,13 +2802,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2911,13 +2819,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2928,30 +2836,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2962,30 +2870,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2996,13 +2904,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -3013,30 +2921,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -3047,13 +2955,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3081,7 +2989,7 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>47</x:v>
@@ -3093,12 +3001,12 @@
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>47</x:v>
@@ -3110,7 +3018,7 @@
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
@@ -3132,7 +3040,7 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
         <x:v>16</x:v>
@@ -3144,7 +3052,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
@@ -3166,10 +3074,10 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>17</x:v>
@@ -3178,15 +3086,15 @@
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>17</x:v>
@@ -3195,15 +3103,15 @@
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>17</x:v>
@@ -3217,10 +3125,10 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>17</x:v>
@@ -3234,10 +3142,10 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>17</x:v>
@@ -3251,24 +3159,24 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>36</x:v>
@@ -3280,7 +3188,7 @@
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
@@ -3302,13 +3210,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>5734395</x:v>
@@ -3319,7 +3227,7 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>10</x:v>
@@ -3331,12 +3239,12 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>10</x:v>
@@ -3345,7 +3253,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>50000</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>12</x:v>
@@ -3362,7 +3270,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>10542390</x:v>
+        <x:v>10542389</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>12</x:v>
@@ -3370,10 +3278,10 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>11</x:v>
@@ -3404,33 +3312,33 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>685625</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>12</x:v>
@@ -3438,13 +3346,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>2651</x:v>
@@ -3455,13 +3363,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>600000</x:v>
@@ -3472,30 +3380,30 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>198972</x:v>
@@ -3506,13 +3414,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>938</x:v>
@@ -3523,13 +3431,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>1974</x:v>
@@ -3540,16 +3448,16 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>1217574</x:v>
+        <x:v>1217575</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>12</x:v>
@@ -3557,13 +3465,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>382</x:v>
@@ -3574,30 +3482,30 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>253656</x:v>
@@ -3608,30 +3516,30 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>408441</x:v>
@@ -3659,10 +3567,10 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>40</x:v>
@@ -3671,15 +3579,15 @@
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>40</x:v>
@@ -3693,13 +3601,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3710,13 +3618,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3727,10 +3635,10 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>45</x:v>
@@ -3739,15 +3647,15 @@
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>45</x:v>
@@ -3761,7 +3669,7 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
         <x:v>44</x:v>
@@ -3773,7 +3681,7 @@
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
@@ -3795,13 +3703,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>-62727</x:v>
@@ -3812,13 +3720,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>214831</x:v>
@@ -3829,13 +3737,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>382</x:v>
@@ -3889,7 +3797,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3903,7 +3811,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3914,10 +3822,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3928,10 +3836,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3942,10 +3850,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3956,24 +3864,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3984,24 +3892,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -4012,10 +3920,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -4026,24 +3934,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4057,7 +3965,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4091,7 +3999,7 @@
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
@@ -4119,7 +4027,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -4138,7 +4046,7 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>17</x:v>
@@ -4147,12 +4055,12 @@
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>17</x:v>
@@ -4169,13 +4077,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
@@ -4189,7 +4097,7 @@
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
@@ -4208,10 +4116,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>5734395</x:v>
@@ -4231,7 +4139,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
@@ -4242,7 +4150,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>10592390</x:v>
+        <x:v>10562693</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>12</x:v>
@@ -4250,7 +4158,7 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>11</x:v>
@@ -4281,13 +4189,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
@@ -4295,10 +4203,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>685625</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
         <x:v>12</x:v>
@@ -4309,7 +4217,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>2651</x:v>
@@ -4323,7 +4231,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>600000</x:v>
@@ -4337,13 +4245,13 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
@@ -4351,7 +4259,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>198972</x:v>
@@ -4365,7 +4273,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>938</x:v>
@@ -4379,10 +4287,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>1219930</x:v>
+        <x:v>1219931</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>12</x:v>
@@ -4393,13 +4301,13 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
@@ -4407,7 +4315,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>253656</x:v>
@@ -4418,24 +4326,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>408441</x:v>
@@ -4460,7 +4368,7 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>40</x:v>
@@ -4469,12 +4377,12 @@
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>40</x:v>
@@ -4491,7 +4399,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4505,7 +4413,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4516,7 +4424,7 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
         <x:v>45</x:v>
@@ -4525,12 +4433,12 @@
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>45</x:v>
@@ -4553,7 +4461,7 @@
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
@@ -4575,7 +4483,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>-62727</x:v>
@@ -4589,7 +4497,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>214831</x:v>
@@ -4603,7 +4511,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>382</x:v>
@@ -4650,7 +4558,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4661,18 +4569,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4683,7 +4591,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4700,7 +4608,7 @@
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -4716,13 +4624,13 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
@@ -4733,7 +4641,7 @@
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
@@ -4749,7 +4657,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>5734395</x:v>
@@ -4766,7 +4674,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -4774,7 +4682,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>10592772</x:v>
+        <x:v>10563075</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>12</x:v>
@@ -4793,21 +4701,21 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2435145</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>685625</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>12</x:v>
@@ -4815,7 +4723,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>602651</x:v>
@@ -4826,18 +4734,18 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>198972</x:v>
@@ -4848,10 +4756,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>1220868</x:v>
+        <x:v>1220869</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>12</x:v>
@@ -4859,18 +4767,18 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>662097</x:v>
@@ -4887,7 +4795,7 @@
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
@@ -4903,7 +4811,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>764</x:v>
@@ -4920,7 +4828,7 @@
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
@@ -4936,7 +4844,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>-62727</x:v>
@@ -4947,7 +4855,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>214831</x:v>
@@ -4958,7 +4866,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>382</x:v>
@@ -5001,7 +4909,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5009,7 +4917,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -5017,7 +4925,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5033,7 +4941,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-6917</x:v>
@@ -5049,7 +4957,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>5734395</x:v>
@@ -5060,7 +4968,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>30732677</x:v>
+        <x:v>30702980</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
@@ -5073,15 +4981,15 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>3120770</x:v>
+        <x:v>3120776</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>602651</x:v>
@@ -5089,7 +4997,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>399814</x:v>
@@ -5097,15 +5005,15 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1220868</x:v>
+        <x:v>1220869</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>5315931</x:v>
@@ -5121,7 +5029,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>764</x:v>
@@ -5137,7 +5045,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>-62727</x:v>
@@ -5145,7 +5053,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>214831</x:v>
@@ -5153,7 +5061,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -5197,10 +5105,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5208,10 +5116,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5222,7 +5130,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5230,10 +5138,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5241,10 +5149,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5252,10 +5160,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5266,7 +5174,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5274,7 +5182,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>17</x:v>
@@ -5285,7 +5193,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>17</x:v>
@@ -5307,7 +5215,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>17</x:v>
@@ -5318,7 +5226,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>17</x:v>
@@ -5329,7 +5237,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>17</x:v>
@@ -5340,7 +5248,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>17</x:v>
@@ -5351,10 +5259,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>-6917</x:v>
@@ -5373,7 +5281,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>37</x:v>
@@ -5387,7 +5295,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>382</x:v>
@@ -5395,10 +5303,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5734013</x:v>
@@ -5417,13 +5325,13 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>50000</x:v>
+        <x:v>20304</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
@@ -5439,13 +5347,13 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>30638642</x:v>
+        <x:v>30638641</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
@@ -5461,21 +5369,21 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>3120770</x:v>
+        <x:v>3120776</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>600000</x:v>
@@ -5486,7 +5394,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2651</x:v>
@@ -5497,7 +5405,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1870</x:v>
@@ -5505,10 +5413,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>397944</x:v>
@@ -5516,13 +5424,13 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>1217574</x:v>
+        <x:v>1217575</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
@@ -5530,7 +5438,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>3294</x:v>
@@ -5538,10 +5446,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>603656</x:v>
@@ -5552,7 +5460,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>58441</x:v>
@@ -5560,10 +5468,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>4653834</x:v>
@@ -5593,7 +5501,7 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>40</x:v>
@@ -5607,7 +5515,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>764</x:v>
@@ -5626,7 +5534,7 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
         <x:v>45</x:v>
@@ -5637,7 +5545,7 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>45</x:v>
@@ -5651,7 +5559,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-62727</x:v>
@@ -5659,10 +5567,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>214831</x:v>
@@ -5673,7 +5581,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,37 +42,343 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
     <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
     <x:t>CRAIG, ANGIE</x:t>
@@ -81,319 +387,13 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCADAMS, BEN</x:t>
   </x:si>
   <x:si>
     <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -882,7 +882,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>10000</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -905,7 +905,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>382</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -913,22 +913,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -936,22 +936,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>685627</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -959,22 +959,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>214831</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -982,22 +982,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>4383748</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1005,22 +1005,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1028,45 +1028,45 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>3515615</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1074,91 +1074,91 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>382</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>164138</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>4968501</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>579319</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1166,68 +1166,68 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F15" s="1">
-        <x:v>3515616</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>500000</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>382</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1235,206 +1235,206 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>1870</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F19" s="1">
-        <x:v>2000000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>-9678</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>5734013</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>20139905</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>60000</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>152765</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>198972</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>253656</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1442,68 +1442,68 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>350000</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1183678</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>108000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1511,45 +1511,45 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B30" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
+      <x:c r="D30" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>1183678</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>715</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1557,22 +1557,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>938</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1580,68 +1580,68 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>63298</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>600000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>3985698</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1649,22 +1649,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>825294</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1672,22 +1672,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>3985700</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1695,45 +1695,45 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F38" s="1">
-        <x:v>362844</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>333</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1741,91 +1741,91 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>382</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>3575107</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>59748</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>-28160</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1833,22 +1833,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>39386</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1856,22 +1856,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>198972</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1879,22 +1879,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4379243</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1902,68 +1902,68 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>3232621</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>2326917</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1971,45 +1971,45 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>333</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1974</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2017,91 +2017,91 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D52" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="F52" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-46</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>2326917</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>499160</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2109,91 +2109,91 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>1642139</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>663879</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="F59" s="1">
-        <x:v>-62727</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2201,22 +2201,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>382</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2224,22 +2224,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>33653</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2247,10 +2247,10 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>110</x:v>
@@ -2262,7 +2262,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2270,45 +2270,45 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-6917</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
+      <x:c r="E64" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E64" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F64" s="1">
-        <x:v>149773</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2316,22 +2316,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>20304</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2339,22 +2339,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E66" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E66" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F66" s="1">
-        <x:v>104555</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2362,22 +2362,22 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>253750</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2385,91 +2385,91 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="D68" s="1" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>104555</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>382</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>382</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>58441</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2477,114 +2477,114 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>382</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>14264</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>382</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>2435149</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>10498736</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2592,22 +2592,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>500346</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2615,22 +2615,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>651087</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2638,45 +2638,45 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>1426379</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>566488</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2684,25 +2684,25 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2751,13 +2751,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2768,13 +2768,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2785,13 +2785,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2802,13 +2802,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2819,13 +2819,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2836,30 +2836,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2870,30 +2870,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2904,13 +2904,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2921,30 +2921,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2955,13 +2955,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -2972,13 +2972,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>8758871</x:v>
@@ -2989,47 +2989,47 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>4968501</x:v>
@@ -3040,30 +3040,30 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>7971780</x:v>
@@ -3074,47 +3074,47 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>209110</x:v>
@@ -3125,13 +3125,13 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>149773</x:v>
@@ -3142,13 +3142,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>9267843</x:v>
@@ -3159,47 +3159,47 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7610550</x:v>
@@ -3210,13 +3210,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>5734395</x:v>
@@ -3227,30 +3227,30 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20304</x:v>
@@ -3261,13 +3261,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>10542389</x:v>
@@ -3278,13 +3278,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>382</x:v>
@@ -3295,13 +3295,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>2649</x:v>
@@ -3312,30 +3312,30 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>685627</x:v>
@@ -3346,10 +3346,10 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>84</x:v>
@@ -3363,10 +3363,10 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>84</x:v>
@@ -3380,30 +3380,30 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>198972</x:v>
@@ -3414,13 +3414,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>938</x:v>
@@ -3431,13 +3431,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>1974</x:v>
@@ -3448,13 +3448,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1217575</x:v>
@@ -3465,13 +3465,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>382</x:v>
@@ -3482,30 +3482,30 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>253656</x:v>
@@ -3516,30 +3516,30 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>408441</x:v>
@@ -3550,13 +3550,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>11995</x:v>
@@ -3567,30 +3567,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>382</x:v>
@@ -3601,13 +3601,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3618,13 +3618,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3635,30 +3635,30 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>39386</x:v>
@@ -3669,30 +3669,30 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>164138</x:v>
@@ -3703,13 +3703,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>-62727</x:v>
@@ -3720,13 +3720,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>214831</x:v>
@@ -3737,13 +3737,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>382</x:v>
@@ -3794,10 +3794,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3808,10 +3808,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3822,10 +3822,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3836,10 +3836,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3850,10 +3850,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3864,24 +3864,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3892,24 +3892,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3920,10 +3920,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3934,24 +3934,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -3962,10 +3962,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -3976,10 +3976,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>8758871</x:v>
@@ -3990,24 +3990,24 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>4968501</x:v>
@@ -4018,24 +4018,24 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>7971780</x:v>
@@ -4046,24 +4046,24 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>9626726</x:v>
@@ -4074,38 +4074,38 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7610550</x:v>
@@ -4116,10 +4116,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>5734395</x:v>
@@ -4130,24 +4130,24 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>10562693</x:v>
@@ -4158,10 +4158,10 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>382</x:v>
@@ -4172,10 +4172,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2649</x:v>
@@ -4186,24 +4186,24 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>685627</x:v>
@@ -4214,7 +4214,7 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>84</x:v>
@@ -4228,7 +4228,7 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>84</x:v>
@@ -4242,24 +4242,24 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>198972</x:v>
@@ -4270,10 +4270,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>938</x:v>
@@ -4284,10 +4284,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>1219931</x:v>
@@ -4298,24 +4298,24 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>253656</x:v>
@@ -4326,24 +4326,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>408441</x:v>
@@ -4354,10 +4354,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>11995</x:v>
@@ -4368,24 +4368,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>
@@ -4396,10 +4396,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4410,10 +4410,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4424,24 +4424,24 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>39386</x:v>
@@ -4452,24 +4452,24 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>164138</x:v>
@@ -4480,10 +4480,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>-62727</x:v>
@@ -4494,10 +4494,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>214831</x:v>
@@ -4508,10 +4508,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>382</x:v>
@@ -4558,7 +4558,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4569,18 +4569,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4591,7 +4591,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4602,18 +4602,18 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>31325878</x:v>
@@ -4624,29 +4624,29 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7610550</x:v>
@@ -4657,7 +4657,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>5734395</x:v>
@@ -4668,18 +4668,18 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>10563075</x:v>
@@ -4690,7 +4690,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>2649</x:v>
@@ -4701,18 +4701,18 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>685627</x:v>
@@ -4734,18 +4734,18 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>198972</x:v>
@@ -4756,7 +4756,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1220869</x:v>
@@ -4767,18 +4767,18 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>662097</x:v>
@@ -4789,18 +4789,18 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>12377</x:v>
@@ -4811,7 +4811,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>764</x:v>
@@ -4822,18 +4822,18 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>203524</x:v>
@@ -4844,7 +4844,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>-62727</x:v>
@@ -4855,7 +4855,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>214831</x:v>
@@ -4866,7 +4866,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>382</x:v>
@@ -4909,7 +4909,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4917,7 +4917,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -4925,7 +4925,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -4933,7 +4933,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>37923820</x:v>
@@ -4941,7 +4941,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-6917</x:v>
@@ -4949,7 +4949,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14781122</x:v>
@@ -4957,7 +4957,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>5734395</x:v>
@@ -4965,7 +4965,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>30702980</x:v>
@@ -4973,7 +4973,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>2649</x:v>
@@ -4981,7 +4981,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3120776</x:v>
@@ -4997,7 +4997,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>399814</x:v>
@@ -5005,7 +5005,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1220869</x:v>
@@ -5013,7 +5013,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>5315931</x:v>
@@ -5021,7 +5021,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>-18676</x:v>
@@ -5029,7 +5029,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>764</x:v>
@@ -5037,7 +5037,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>217742</x:v>
@@ -5045,7 +5045,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>-62727</x:v>
@@ -5053,7 +5053,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>214831</x:v>
@@ -5061,7 +5061,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -5105,10 +5105,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5116,10 +5116,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5127,10 +5127,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5138,10 +5138,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5149,10 +5149,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5160,10 +5160,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5171,10 +5171,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5182,10 +5182,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>8758489</x:v>
@@ -5193,10 +5193,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3904224</x:v>
@@ -5204,10 +5204,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>764</x:v>
@@ -5215,10 +5215,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>500346</x:v>
@@ -5226,10 +5226,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>19591653</x:v>
@@ -5237,10 +5237,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>149773</x:v>
@@ -5248,10 +5248,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>5018571</x:v>
@@ -5259,10 +5259,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>-6917</x:v>
@@ -5270,10 +5270,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>10626696</x:v>
@@ -5281,10 +5281,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4154426</x:v>
@@ -5292,10 +5292,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>382</x:v>
@@ -5303,10 +5303,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5734013</x:v>
@@ -5314,10 +5314,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>34035</x:v>
@@ -5325,10 +5325,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>20304</x:v>
@@ -5336,10 +5336,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>10000</x:v>
@@ -5347,10 +5347,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>30638641</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>2649</x:v>
@@ -5369,10 +5369,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3120776</x:v>
@@ -5380,7 +5380,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>84</x:v>
@@ -5391,7 +5391,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>84</x:v>
@@ -5402,10 +5402,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1870</x:v>
@@ -5413,10 +5413,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>397944</x:v>
@@ -5424,10 +5424,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1217575</x:v>
@@ -5435,10 +5435,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>3294</x:v>
@@ -5446,10 +5446,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>603656</x:v>
@@ -5457,10 +5457,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>58441</x:v>
@@ -5468,10 +5468,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>4653834</x:v>
@@ -5479,10 +5479,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>382</x:v>
@@ -5490,10 +5490,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>11995</x:v>
@@ -5501,10 +5501,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>-31053</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>764</x:v>
@@ -5523,10 +5523,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>178402</x:v>
@@ -5534,10 +5534,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>39386</x:v>
@@ -5545,10 +5545,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>-46</x:v>
@@ -5556,10 +5556,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-62727</x:v>
@@ -5567,10 +5567,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>214831</x:v>
@@ -5578,10 +5578,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,12 +42,153 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
     <x:t>RJC VICTORY FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
@@ -57,15 +198,6 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOLDMAN, DANIEL</x:t>
   </x:si>
   <x:si>
@@ -75,21 +207,9 @@
     <x:t>NY</x:t>
   </x:si>
   <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
@@ -99,39 +219,93 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
   </x:si>
   <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOSS, JEREMY</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
@@ -147,66 +321,21 @@
     <x:t>COLLINS, KINA</x:t>
   </x:si>
   <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
     <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>WAHAB, AISHA</x:t>
   </x:si>
   <x:si>
@@ -222,12 +351,6 @@
     <x:t>COGNETTI, PAIGE</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
@@ -255,114 +378,6 @@
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
   </x:si>
   <x:si>
@@ -379,21 +394,6 @@
   </x:si>
   <x:si>
     <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -882,7 +882,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>3515615</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -905,7 +905,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -913,22 +913,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>382</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -936,22 +936,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>164138</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -959,22 +959,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="C6" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>4968501</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -982,22 +982,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>579319</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1005,22 +1005,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1028,42 +1028,42 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>500000</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1">
         <x:v>382</x:v>
@@ -1074,91 +1074,91 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1870</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>2000000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>-9678</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>5734013</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1166,45 +1166,45 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>20139905</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>60000</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1212,22 +1212,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>152765</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1235,45 +1235,45 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
+      <x:c r="C18" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>198972</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>253656</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1281,22 +1281,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>350000</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1304,45 +1304,45 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>108000</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1350,68 +1350,68 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>362844</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>333</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1419,22 +1419,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>382</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1442,68 +1442,68 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>3575107</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>59748</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-28160</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1511,22 +1511,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>39386</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1534,22 +1534,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F31" s="1">
-        <x:v>198972</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1557,22 +1557,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>4379243</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1580,68 +1580,68 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>3232621</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>4379246</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1649,22 +1649,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-62727</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1672,45 +1672,45 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>382</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>33653</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1718,68 +1718,68 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>2651</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-6917</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>149773</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1787,22 +1787,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>20304</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1810,45 +1810,45 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>253750</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1856,65 +1856,65 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>104555</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>382</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F47" s="1">
         <x:v>382</x:v>
@@ -1925,91 +1925,91 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>58441</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>382</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>14264</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>382</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2017,45 +2017,45 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>2435149</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>10498736</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2063,22 +2063,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>500346</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2086,68 +2086,68 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>651087</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>1426379</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>566488</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2155,45 +2155,45 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1426379</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>715</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2201,68 +2201,68 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>938</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>63298</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>600000</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2270,22 +2270,22 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>3985698</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2293,68 +2293,68 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>825294</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>3985700</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>333</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2362,22 +2362,22 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>1974</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2385,252 +2385,252 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-31053</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>-46</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>499160</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1642139</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>663879</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>10000</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>382</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>2649</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B78" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>685627</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2638,71 +2638,71 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>214831</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>4383748</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>4383749</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2751,13 +2751,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2768,13 +2768,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2785,13 +2785,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2802,13 +2802,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2819,13 +2819,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2836,30 +2836,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2870,30 +2870,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2904,13 +2904,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2921,30 +2921,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2955,13 +2955,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -2972,13 +2972,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>8758871</x:v>
@@ -2989,47 +2989,47 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>4968501</x:v>
@@ -3040,30 +3040,30 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>7971780</x:v>
@@ -3074,47 +3074,47 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>209110</x:v>
@@ -3125,13 +3125,13 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>149773</x:v>
@@ -3142,13 +3142,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>9267843</x:v>
@@ -3159,47 +3159,47 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7610550</x:v>
@@ -3210,13 +3210,13 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>5734395</x:v>
@@ -3227,30 +3227,30 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20304</x:v>
@@ -3261,13 +3261,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>10542389</x:v>
@@ -3278,13 +3278,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>382</x:v>
@@ -3295,13 +3295,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>2649</x:v>
@@ -3312,30 +3312,30 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>685627</x:v>
@@ -3346,13 +3346,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>2651</x:v>
@@ -3363,13 +3363,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>600000</x:v>
@@ -3380,30 +3380,30 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>198972</x:v>
@@ -3414,13 +3414,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>938</x:v>
@@ -3431,13 +3431,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>1974</x:v>
@@ -3448,13 +3448,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1217575</x:v>
@@ -3465,13 +3465,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>382</x:v>
@@ -3482,30 +3482,30 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>253656</x:v>
@@ -3516,30 +3516,30 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>408441</x:v>
@@ -3550,13 +3550,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>11995</x:v>
@@ -3567,30 +3567,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>382</x:v>
@@ -3601,13 +3601,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3618,13 +3618,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3635,30 +3635,30 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>39386</x:v>
@@ -3669,30 +3669,30 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>164138</x:v>
@@ -3703,13 +3703,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>-62727</x:v>
@@ -3720,13 +3720,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>214831</x:v>
@@ -3737,13 +3737,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>382</x:v>
@@ -3794,10 +3794,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3808,10 +3808,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3822,10 +3822,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3836,10 +3836,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3850,10 +3850,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3864,24 +3864,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3892,24 +3892,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3920,10 +3920,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3934,24 +3934,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -3962,10 +3962,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -3976,10 +3976,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>8758871</x:v>
@@ -3990,24 +3990,24 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>4968501</x:v>
@@ -4018,24 +4018,24 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>7971780</x:v>
@@ -4046,24 +4046,24 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>9626726</x:v>
@@ -4074,38 +4074,38 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7610550</x:v>
@@ -4116,10 +4116,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>5734395</x:v>
@@ -4130,24 +4130,24 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>10562693</x:v>
@@ -4158,10 +4158,10 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>382</x:v>
@@ -4172,10 +4172,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2649</x:v>
@@ -4186,24 +4186,24 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>685627</x:v>
@@ -4214,10 +4214,10 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>2651</x:v>
@@ -4228,10 +4228,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>600000</x:v>
@@ -4242,24 +4242,24 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>198972</x:v>
@@ -4270,10 +4270,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>938</x:v>
@@ -4284,10 +4284,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>1219931</x:v>
@@ -4298,24 +4298,24 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>253656</x:v>
@@ -4326,24 +4326,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>408441</x:v>
@@ -4354,10 +4354,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>11995</x:v>
@@ -4368,24 +4368,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>382</x:v>
@@ -4396,10 +4396,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4410,10 +4410,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4424,24 +4424,24 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>39386</x:v>
@@ -4452,24 +4452,24 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>164138</x:v>
@@ -4480,10 +4480,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>-62727</x:v>
@@ -4494,10 +4494,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>214831</x:v>
@@ -4508,10 +4508,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>382</x:v>
@@ -4558,7 +4558,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4569,18 +4569,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4591,7 +4591,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4602,18 +4602,18 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>31325878</x:v>
@@ -4624,29 +4624,29 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7610550</x:v>
@@ -4657,7 +4657,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>5734395</x:v>
@@ -4668,18 +4668,18 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>10563075</x:v>
@@ -4690,7 +4690,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>2649</x:v>
@@ -4701,18 +4701,18 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>685627</x:v>
@@ -4723,7 +4723,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>602651</x:v>
@@ -4734,18 +4734,18 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>198972</x:v>
@@ -4756,7 +4756,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1220869</x:v>
@@ -4767,18 +4767,18 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>662097</x:v>
@@ -4789,18 +4789,18 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>12377</x:v>
@@ -4811,7 +4811,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>764</x:v>
@@ -4822,18 +4822,18 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>203524</x:v>
@@ -4844,7 +4844,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>-62727</x:v>
@@ -4855,7 +4855,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>214831</x:v>
@@ -4866,7 +4866,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>382</x:v>
@@ -4909,7 +4909,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4917,7 +4917,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -4925,7 +4925,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -4933,7 +4933,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>37923820</x:v>
@@ -4941,7 +4941,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>-6917</x:v>
@@ -4949,7 +4949,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>14781122</x:v>
@@ -4957,7 +4957,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>5734395</x:v>
@@ -4965,7 +4965,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>30702980</x:v>
@@ -4973,7 +4973,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>2649</x:v>
@@ -4981,7 +4981,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>3120776</x:v>
@@ -4989,7 +4989,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>602651</x:v>
@@ -4997,7 +4997,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>399814</x:v>
@@ -5005,7 +5005,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1220869</x:v>
@@ -5013,7 +5013,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>5315931</x:v>
@@ -5021,7 +5021,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>-18676</x:v>
@@ -5029,7 +5029,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>764</x:v>
@@ -5037,7 +5037,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>217742</x:v>
@@ -5045,7 +5045,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>-62727</x:v>
@@ -5053,7 +5053,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>214831</x:v>
@@ -5061,7 +5061,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>382</x:v>
@@ -5105,10 +5105,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5116,10 +5116,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5127,10 +5127,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5138,10 +5138,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5149,10 +5149,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5160,10 +5160,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5171,10 +5171,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5182,10 +5182,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>8758489</x:v>
@@ -5193,10 +5193,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3904224</x:v>
@@ -5204,10 +5204,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>764</x:v>
@@ -5215,10 +5215,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>500346</x:v>
@@ -5226,10 +5226,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>19591653</x:v>
@@ -5237,10 +5237,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>149773</x:v>
@@ -5248,10 +5248,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>5018571</x:v>
@@ -5259,10 +5259,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>-6917</x:v>
@@ -5270,10 +5270,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>10626696</x:v>
@@ -5281,10 +5281,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4154426</x:v>
@@ -5292,10 +5292,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>382</x:v>
@@ -5303,10 +5303,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>5734013</x:v>
@@ -5314,10 +5314,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>34035</x:v>
@@ -5325,10 +5325,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>20304</x:v>
@@ -5336,10 +5336,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>10000</x:v>
@@ -5347,10 +5347,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>30638641</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>2649</x:v>
@@ -5369,10 +5369,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>3120776</x:v>
@@ -5380,10 +5380,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>600000</x:v>
@@ -5391,10 +5391,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2651</x:v>
@@ -5402,10 +5402,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>1870</x:v>
@@ -5413,10 +5413,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>397944</x:v>
@@ -5424,10 +5424,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1217575</x:v>
@@ -5435,10 +5435,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>3294</x:v>
@@ -5446,10 +5446,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>603656</x:v>
@@ -5457,10 +5457,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>58441</x:v>
@@ -5468,10 +5468,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>4653834</x:v>
@@ -5479,10 +5479,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>382</x:v>
@@ -5490,10 +5490,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>11995</x:v>
@@ -5501,10 +5501,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>-31053</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>764</x:v>
@@ -5523,10 +5523,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>178402</x:v>
@@ -5534,10 +5534,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>39386</x:v>
@@ -5545,10 +5545,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>-46</x:v>
@@ -5556,10 +5556,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-62727</x:v>
@@ -5567,10 +5567,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>214831</x:v>
@@ -5578,10 +5578,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -126,6 +126,96 @@
     <x:t>RJC VICTORY FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>TRUMP, DONALD J.</x:t>
   </x:si>
   <x:si>
@@ -135,27 +225,18 @@
     <x:t>LURIA, ELAINE</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
     <x:t>VA</x:t>
   </x:si>
   <x:si>
     <x:t>COOPER, ROY</x:t>
   </x:si>
   <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>HOSTETTLER, JOHN N</x:t>
   </x:si>
   <x:si>
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
@@ -177,108 +258,135 @@
     <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>PELTOLA, MARY</x:t>
   </x:si>
   <x:si>
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
     <x:t>STELSON, JANELLE</x:t>
   </x:si>
   <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONLEY, CAIT</x:t>
   </x:si>
   <x:si>
@@ -295,105 +403,6 @@
   </x:si>
   <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -464,8 +473,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G81" totalsRowShown="0">
-  <x:autoFilter ref="A1:G81"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
+  <x:autoFilter ref="A1:G82"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -480,8 +489,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E60" totalsRowShown="0">
-  <x:autoFilter ref="A1:E60"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E61" totalsRowShown="0">
+  <x:autoFilter ref="A1:E61"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -494,8 +503,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D53" totalsRowShown="0">
-  <x:autoFilter ref="A1:D53"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D54" totalsRowShown="0">
+  <x:autoFilter ref="A1:D54"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -507,8 +516,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C30" totalsRowShown="0">
-  <x:autoFilter ref="A1:C30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C31" totalsRowShown="0">
+  <x:autoFilter ref="A1:C31"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -519,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B21" totalsRowShown="0">
-  <x:autoFilter ref="A1:B21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B22" totalsRowShown="0">
+  <x:autoFilter ref="A1:B22"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -530,8 +539,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C45" totalsRowShown="0">
-  <x:autoFilter ref="A1:C45"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C46" totalsRowShown="0">
+  <x:autoFilter ref="A1:C46"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -829,7 +838,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G81"/>
+  <x:dimension ref="A1:G82"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1037,13 +1046,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>-62727</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1051,22 +1060,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>382</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1080,16 +1089,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>33653</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1103,16 +1112,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>2651</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1126,39 +1135,39 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>-6917</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>149773</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1166,22 +1175,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>20304</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1189,22 +1198,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>104555</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1212,22 +1221,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>253750</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1235,22 +1244,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>104555</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1258,22 +1267,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>3515615</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1281,22 +1290,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>11995</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1304,22 +1313,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>382</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1327,45 +1336,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>164138</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>4968501</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1373,22 +1382,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>579319</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1396,22 +1405,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>3515616</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1425,16 +1434,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>715</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1448,16 +1457,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>938</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1465,45 +1474,45 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>63298</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>600000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1511,22 +1520,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>3985698</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1534,22 +1543,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>825294</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1557,22 +1566,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>3985700</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1580,22 +1589,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>382</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1609,19 +1618,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>382</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
@@ -1638,10 +1647,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1655,19 +1664,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F36" s="1">
-        <x:v>382</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
@@ -1678,42 +1687,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>14264</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>382</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1727,16 +1736,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>2435149</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
@@ -1747,7 +1756,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
         <x:v>10</x:v>
@@ -1756,30 +1765,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>10498736</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>500346</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1787,22 +1796,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>651087</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1810,25 +1819,25 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>1426379</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
@@ -1839,16 +1848,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>566488</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1856,68 +1865,68 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>1426379</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>500000</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>382</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1925,91 +1934,91 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1870</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>2000000</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>-9678</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>5734013</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2023,62 +2032,62 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>20139905</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>60000</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>152765</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2086,45 +2095,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>198972</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>253656</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2132,22 +2141,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2155,94 +2164,94 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>108000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1183678</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>362844</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
@@ -2253,16 +2262,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>333</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2270,25 +2279,25 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
@@ -2299,19 +2308,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>3575107</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
@@ -2322,39 +2331,39 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>59748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-28160</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2362,137 +2371,137 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>39386</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>198972</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4379243</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>3232621</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>4379246</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2506,16 +2515,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>333</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>12</x:v>
@@ -2529,42 +2538,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>1974</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
@@ -2575,19 +2584,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-46</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
@@ -2598,39 +2607,39 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>2326917</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>499160</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2638,71 +2647,94 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>663879</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>1642139</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F81" s="1">
+        <x:v>566488</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:7">
+      <x:c r="A82" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C82" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D82" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E82" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F81" s="1">
-        <x:v>663879</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="s">
-        <x:v>44</x:v>
+      <x:c r="F82" s="1">
+        <x:v>1426379</x:v>
+      </x:c>
+      <x:c r="G82" s="1" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2721,7 +2753,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E60"/>
+  <x:dimension ref="A1:E61"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2751,13 +2783,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2768,13 +2800,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2785,13 +2817,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2802,13 +2834,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2819,13 +2851,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2836,30 +2868,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2870,30 +2902,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2904,13 +2936,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2921,30 +2953,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2955,13 +2987,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -2972,92 +3004,92 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1">
-        <x:v>8758871</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1">
-        <x:v>-9678</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
-        <x:v>59748</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D19" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
@@ -3066,32 +3098,32 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D21" s="1">
-        <x:v>2367356</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>32</x:v>
@@ -3100,15 +3132,15 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="1">
-        <x:v>2852758</x:v>
+        <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>32</x:v>
@@ -3117,15 +3149,15 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="1">
-        <x:v>209110</x:v>
+        <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
@@ -3134,7 +3166,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D24" s="1">
-        <x:v>149773</x:v>
+        <x:v>209110</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>12</x:v>
@@ -3142,7 +3174,7 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
@@ -3151,7 +3183,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="D25" s="1">
-        <x:v>9267843</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>12</x:v>
@@ -3159,67 +3191,67 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D26" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9267843</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D29" s="1">
-        <x:v>5734395</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>12</x:v>
@@ -3227,24 +3259,24 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D30" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>10</x:v>
@@ -3253,15 +3285,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>20304</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>10</x:v>
@@ -3270,7 +3302,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
-        <x:v>10542389</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>12</x:v>
@@ -3278,16 +3310,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>382</x:v>
+        <x:v>10542389</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>12</x:v>
@@ -3295,16 +3327,16 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D34" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
         <x:v>12</x:v>
@@ -3312,24 +3344,24 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D35" s="1">
-        <x:v>2435149</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>23</x:v>
@@ -3338,24 +3370,24 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
-        <x:v>685627</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
-        <x:v>2651</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>12</x:v>
@@ -3363,16 +3395,16 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D38" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>12</x:v>
@@ -3380,50 +3412,50 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D39" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D40" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D41" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
         <x:v>12</x:v>
@@ -3431,16 +3463,16 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D42" s="1">
-        <x:v>1974</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
         <x:v>12</x:v>
@@ -3448,16 +3480,16 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D43" s="1">
-        <x:v>1217575</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>12</x:v>
@@ -3465,16 +3497,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>382</x:v>
+        <x:v>1217575</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>12</x:v>
@@ -3482,84 +3514,84 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D45" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D46" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D47" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D48" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="1">
-        <x:v>11995</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
         <x:v>12</x:v>
@@ -3567,47 +3599,47 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3618,13 +3650,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3638,81 +3670,81 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D56" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D57" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D58" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>12</x:v>
@@ -3720,16 +3752,16 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D59" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>12</x:v>
@@ -3737,18 +3769,35 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D60" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:5">
+      <x:c r="A61" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D61" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E60" s="1" t="s">
+      <x:c r="E61" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3768,7 +3817,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D53"/>
+  <x:dimension ref="A1:D54"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3797,7 +3846,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3808,10 +3857,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3822,10 +3871,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3839,7 +3888,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3850,10 +3899,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3864,24 +3913,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3892,24 +3941,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3920,10 +3969,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3934,24 +3983,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -3965,7 +4014,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -3976,58 +4025,58 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>8758871</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>50070</x:v>
+        <x:v>8758871</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>4968501</x:v>
+        <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>1327758</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
@@ -4038,24 +4087,24 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>7971780</x:v>
+        <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>5220114</x:v>
+        <x:v>7971780</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
@@ -4066,63 +4115,63 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>9626726</x:v>
+        <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>-6917</x:v>
+        <x:v>9626726</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>5734395</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
         <x:v>12</x:v>
@@ -4130,16 +4179,16 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
@@ -4150,21 +4199,21 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>10562693</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>382</x:v>
+        <x:v>10562693</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>12</x:v>
@@ -4172,13 +4221,13 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>12</x:v>
@@ -4186,16 +4235,16 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>2435149</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
@@ -4206,21 +4255,21 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>685627</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>2651</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>12</x:v>
@@ -4228,13 +4277,13 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>600000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
         <x:v>12</x:v>
@@ -4242,41 +4291,41 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>200842</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>938</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
         <x:v>12</x:v>
@@ -4284,13 +4333,13 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>1219931</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
         <x:v>12</x:v>
@@ -4298,44 +4347,44 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>2326917</x:v>
+        <x:v>1219931</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>253656</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
@@ -4343,24 +4392,24 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>408441</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>11995</x:v>
+        <x:v>408441</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
         <x:v>12</x:v>
@@ -4368,38 +4417,38 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4410,10 +4459,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4424,69 +4473,69 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
         <x:v>12</x:v>
@@ -4494,13 +4543,13 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>12</x:v>
@@ -4508,15 +4557,29 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C53" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C54" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D53" s="1" t="s">
+      <x:c r="D54" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4536,7 +4599,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C30"/>
+  <x:dimension ref="A1:C31"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4558,7 +4621,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4569,18 +4632,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4591,7 +4654,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4602,13 +4665,13 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>6597942</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -4616,51 +4679,51 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>31325878</x:v>
+        <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>-6917</x:v>
+        <x:v>31325878</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>7170572</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>7610550</x:v>
+        <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>5734395</x:v>
+        <x:v>7610550</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>12</x:v>
@@ -4668,13 +4731,13 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>20139905</x:v>
+        <x:v>5734395</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
@@ -4682,18 +4745,18 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>10563075</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>2649</x:v>
+        <x:v>10563075</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4701,13 +4764,13 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>2435149</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -4715,18 +4778,18 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>685627</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>602651</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>12</x:v>
@@ -4734,32 +4797,32 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>200842</x:v>
+        <x:v>602651</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>198972</x:v>
+        <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>1220869</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>12</x:v>
@@ -4767,54 +4830,54 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>4653834</x:v>
+        <x:v>1220869</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>662097</x:v>
+        <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B23" s="1">
-        <x:v>-31053</x:v>
+        <x:v>662097</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>12377</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1">
-        <x:v>764</x:v>
+        <x:v>12377</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>12</x:v>
@@ -4822,32 +4885,32 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>14218</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>203524</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>-62727</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>12</x:v>
@@ -4855,10 +4918,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>12</x:v>
@@ -4866,12 +4929,23 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B30" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:3">
+      <x:c r="A31" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B31" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
+      <x:c r="C31" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4891,7 +4965,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B21"/>
+  <x:dimension ref="A1:B22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4909,7 +4983,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4917,7 +4991,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -4925,7 +4999,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -4933,137 +5007,145 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="1">
-        <x:v>37923820</x:v>
+        <x:v>299290</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1">
-        <x:v>-6917</x:v>
+        <x:v>37923820</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1">
-        <x:v>14781122</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="1">
-        <x:v>5734395</x:v>
+        <x:v>14781122</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B9" s="1">
-        <x:v>30702980</x:v>
+        <x:v>5734395</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>2649</x:v>
+        <x:v>30702980</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1">
-        <x:v>3120776</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
-        <x:v>602651</x:v>
+        <x:v>3120776</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>399814</x:v>
+        <x:v>602651</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>1220869</x:v>
+        <x:v>399814</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>5315931</x:v>
+        <x:v>1220869</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B16" s="1">
-        <x:v>-18676</x:v>
+        <x:v>5315931</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>764</x:v>
+        <x:v>-18676</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>217742</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>-62727</x:v>
+        <x:v>217742</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B20" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:2">
+      <x:c r="A22" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B22" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>
@@ -5083,7 +5165,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C45"/>
+  <x:dimension ref="A1:C46"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5108,7 +5190,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5119,7 +5201,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5130,7 +5212,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5141,7 +5223,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5149,10 +5231,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5163,7 +5245,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5174,7 +5256,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5182,79 +5264,79 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="1">
-        <x:v>8758489</x:v>
+        <x:v>299290</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1">
-        <x:v>3904224</x:v>
+        <x:v>8758489</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="1">
-        <x:v>764</x:v>
+        <x:v>3904224</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
-        <x:v>500346</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
-        <x:v>19591653</x:v>
+        <x:v>500346</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1">
-        <x:v>149773</x:v>
+        <x:v>19591653</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
-        <x:v>5018571</x:v>
+        <x:v>149773</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
@@ -5262,142 +5344,142 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
-        <x:v>-6917</x:v>
+        <x:v>5018571</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C17" s="1">
-        <x:v>10626696</x:v>
+        <x:v>-6917</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>4154426</x:v>
+        <x:v>10626696</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1">
-        <x:v>382</x:v>
+        <x:v>4154426</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C20" s="1">
-        <x:v>5734013</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="1">
-        <x:v>34035</x:v>
+        <x:v>5734013</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
-        <x:v>20304</x:v>
+        <x:v>34035</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
-        <x:v>10000</x:v>
+        <x:v>20304</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
-        <x:v>30638641</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>2649</x:v>
+        <x:v>30638641</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1">
-        <x:v>3120776</x:v>
+        <x:v>2649</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>600000</x:v>
+        <x:v>3120776</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>2651</x:v>
+        <x:v>600000</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
@@ -5405,120 +5487,120 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C29" s="1">
-        <x:v>1870</x:v>
+        <x:v>2651</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C30" s="1">
-        <x:v>397944</x:v>
+        <x:v>1870</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C31" s="1">
-        <x:v>1217575</x:v>
+        <x:v>397944</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>3294</x:v>
+        <x:v>1217575</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="1">
-        <x:v>603656</x:v>
+        <x:v>3294</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C34" s="1">
-        <x:v>58441</x:v>
+        <x:v>603656</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C35" s="1">
-        <x:v>4653834</x:v>
+        <x:v>58441</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C36" s="1">
-        <x:v>382</x:v>
+        <x:v>4653834</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
@@ -5526,64 +5608,75 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C45" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:3">
+      <x:c r="A46" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B45" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C45" s="1">
+      <x:c r="B46" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C46" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -120,6 +120,60 @@
     <x:t>09</x:t>
   </x:si>
   <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -129,9 +183,6 @@
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
@@ -165,55 +216,160 @@
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
     <x:t>TRUMP, DONALD J.</x:t>
@@ -237,24 +393,9 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCMORROW, MALLORY</x:t>
   </x:si>
   <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
@@ -262,147 +403,6 @@
   </x:si>
   <x:si>
     <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1037,22 +1037,22 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>3515615</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1060,22 +1060,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>11995</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1083,22 +1083,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>382</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1106,22 +1106,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>164138</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1129,22 +1129,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>4968501</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1158,16 +1158,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>579319</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1175,45 +1175,45 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>3515616</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>715</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1221,22 +1221,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>938</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1244,22 +1244,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>63298</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1267,22 +1267,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>600000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1290,22 +1290,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>3985698</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1319,16 +1319,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>825294</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1336,45 +1336,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>299290</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3985700</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1382,25 +1382,25 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-62727</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
@@ -1411,16 +1411,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1434,16 +1434,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>33653</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1451,25 +1451,25 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>2651</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
@@ -1483,36 +1483,36 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-6917</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>149773</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1520,22 +1520,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>20304</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1543,22 +1543,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F31" s="1">
-        <x:v>104555</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1566,22 +1566,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>253750</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1589,68 +1589,68 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>104555</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="F34" s="1">
-        <x:v>500000</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>382</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1664,19 +1664,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
@@ -1687,62 +1687,62 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>2000000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>-9678</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>5734013</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1750,45 +1750,45 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>20139905</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>60000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1796,68 +1796,68 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>152765</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>198972</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>253656</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1871,16 +1871,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>350000</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1888,13 +1888,13 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
         <x:v>32</x:v>
@@ -1903,30 +1903,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>1183678</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>108000</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1934,13 +1934,13 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
         <x:v>32</x:v>
@@ -1949,33 +1949,33 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1183678</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>362844</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
@@ -1986,16 +1986,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>333</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2003,25 +2003,25 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
@@ -2032,19 +2032,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>3575107</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
@@ -2055,39 +2055,39 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>59748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>-28160</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2095,140 +2095,140 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>39386</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>198972</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4379243</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>3232621</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
@@ -2239,42 +2239,42 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>333</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>1974</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
@@ -2285,19 +2285,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>-31053</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
@@ -2308,62 +2308,62 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>-46</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2326917</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>499160</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2371,114 +2371,114 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>663879</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>1642139</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>663879</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>382</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>382</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2486,45 +2486,45 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>58441</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>382</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>12</x:v>
@@ -2538,19 +2538,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>14264</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
@@ -2561,16 +2561,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>382</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2578,25 +2578,25 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2435149</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
@@ -2607,30 +2607,30 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>10498736</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
         <x:v>32</x:v>
@@ -2639,7 +2639,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>500346</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2647,22 +2647,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>651087</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2670,13 +2670,13 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
         <x:v>32</x:v>
@@ -2685,30 +2685,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>1426379</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F81" s="1">
-        <x:v>566488</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2716,13 +2716,13 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
         <x:v>32</x:v>
@@ -2731,10 +2731,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>1426379</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2783,13 +2783,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2800,13 +2800,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2817,13 +2817,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2834,13 +2834,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2851,13 +2851,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2868,30 +2868,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2902,30 +2902,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2936,13 +2936,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2953,30 +2953,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2987,13 +2987,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3004,27 +3004,27 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>17</x:v>
@@ -3038,10 +3038,10 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>17</x:v>
@@ -3050,15 +3050,15 @@
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>17</x:v>
@@ -3067,15 +3067,15 @@
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>17</x:v>
@@ -3089,7 +3089,7 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>16</x:v>
@@ -3101,7 +3101,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
@@ -3123,7 +3123,7 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>32</x:v>
@@ -3135,12 +3135,12 @@
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>32</x:v>
@@ -3152,12 +3152,12 @@
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>32</x:v>
@@ -3174,7 +3174,7 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>32</x:v>
@@ -3208,47 +3208,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3259,13 +3259,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3276,7 +3276,7 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>10</x:v>
@@ -3288,12 +3288,12 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>10</x:v>
@@ -3327,10 +3327,10 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>11</x:v>
@@ -3361,7 +3361,7 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>23</x:v>
@@ -3373,7 +3373,7 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
@@ -3395,13 +3395,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3412,13 +3412,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3429,30 +3429,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3463,13 +3463,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3480,13 +3480,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3497,13 +3497,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1217575</x:v>
@@ -3514,13 +3514,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3531,30 +3531,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3565,30 +3565,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3599,13 +3599,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>11995</x:v>
@@ -3616,30 +3616,30 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3650,13 +3650,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3667,13 +3667,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3684,30 +3684,30 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>39386</x:v>
@@ -3718,30 +3718,30 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>164138</x:v>
@@ -3752,13 +3752,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>-62727</x:v>
@@ -3786,13 +3786,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>382</x:v>
@@ -3846,7 +3846,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3857,10 +3857,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3871,10 +3871,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3885,10 +3885,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3899,10 +3899,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3913,24 +3913,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3941,24 +3941,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3969,10 +3969,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3983,24 +3983,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4014,7 +4014,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4025,21 +4025,21 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>17</x:v>
@@ -4053,7 +4053,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>17</x:v>
@@ -4062,12 +4062,12 @@
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>17</x:v>
@@ -4090,7 +4090,7 @@
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
@@ -4118,7 +4118,7 @@
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
@@ -4140,35 +4140,35 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4179,10 +4179,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4202,7 +4202,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
@@ -4221,7 +4221,7 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>11</x:v>
@@ -4258,7 +4258,7 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
@@ -4280,7 +4280,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4291,10 +4291,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4305,24 +4305,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4336,7 +4336,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4350,7 +4350,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1219931</x:v>
@@ -4361,24 +4361,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4389,24 +4389,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4417,10 +4417,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>11995</x:v>
@@ -4431,24 +4431,24 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4462,7 +4462,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4473,10 +4473,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4487,24 +4487,24 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>39386</x:v>
@@ -4515,24 +4515,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>164138</x:v>
@@ -4546,7 +4546,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>-62727</x:v>
@@ -4571,10 +4571,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>382</x:v>
@@ -4621,7 +4621,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4632,18 +4632,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4654,7 +4654,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4665,13 +4665,13 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
@@ -4682,7 +4682,7 @@
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
@@ -4698,29 +4698,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4731,7 +4731,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4748,7 +4748,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -4781,7 +4781,7 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4797,7 +4797,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4808,18 +4808,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4830,7 +4830,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1220869</x:v>
@@ -4841,18 +4841,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4863,18 +4863,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4885,7 +4885,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4896,18 +4896,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4918,7 +4918,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4940,7 +4940,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -4983,7 +4983,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4991,7 +4991,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -4999,7 +4999,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5007,7 +5007,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5023,7 +5023,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5031,7 +5031,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5039,7 +5039,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5071,7 +5071,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5079,7 +5079,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5087,7 +5087,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1220869</x:v>
@@ -5095,7 +5095,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5103,7 +5103,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>-18676</x:v>
@@ -5111,7 +5111,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5119,7 +5119,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5127,7 +5127,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5143,7 +5143,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5187,10 +5187,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5201,7 +5201,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5212,7 +5212,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5220,10 +5220,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5231,10 +5231,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5245,7 +5245,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5256,7 +5256,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5264,10 +5264,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5275,7 +5275,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>17</x:v>
@@ -5286,7 +5286,7 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>17</x:v>
@@ -5308,7 +5308,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>17</x:v>
@@ -5330,7 +5330,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>17</x:v>
@@ -5355,7 +5355,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5363,10 +5363,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5377,7 +5377,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5388,7 +5388,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5399,7 +5399,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5418,7 +5418,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>11</x:v>
@@ -5476,7 +5476,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5487,7 +5487,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5498,7 +5498,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5506,10 +5506,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5520,7 +5520,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1217575</x:v>
@@ -5531,7 +5531,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5542,7 +5542,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5553,7 +5553,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5564,7 +5564,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5575,7 +5575,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -5586,7 +5586,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>11995</x:v>
@@ -5597,7 +5597,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -5608,7 +5608,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>764</x:v>
@@ -5619,7 +5619,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>178402</x:v>
@@ -5627,10 +5627,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>39386</x:v>
@@ -5641,7 +5641,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -5649,10 +5649,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-62727</x:v>
@@ -5674,7 +5674,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,37 +42,352 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
     <x:t>CRAIG, ANGIE</x:t>
@@ -81,328 +396,13 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCADAMS, BEN</x:t>
   </x:si>
   <x:si>
     <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -891,7 +891,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>10000</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -914,7 +914,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>382</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -922,22 +922,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>2649</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -945,22 +945,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>685627</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -968,22 +968,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>214831</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -991,22 +991,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>4383748</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1014,22 +1014,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>4383749</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1037,22 +1037,22 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>715</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1060,22 +1060,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>938</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1083,91 +1083,91 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>63298</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="F12" s="1">
-        <x:v>600000</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>3985698</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>825294</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1175,91 +1175,91 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>299290</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>3515615</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>11995</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1267,22 +1267,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>382</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1290,22 +1290,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>164138</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1313,22 +1313,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>4968501</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1336,22 +1336,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>579319</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1359,22 +1359,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3515616</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1382,45 +1382,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>362844</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>333</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1428,137 +1428,137 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>382</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>3575107</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>59748</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-28160</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>39386</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>198972</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1566,114 +1566,114 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>4379243</x:v>
+        <x:v>20139905</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>3232621</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>2326917</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>4379246</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>382</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1681,22 +1681,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>382</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1704,10 +1704,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>87</x:v>
@@ -1716,33 +1716,33 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>58441</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>382</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1750,91 +1750,91 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>14264</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>382</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>2435149</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>10498736</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1842,91 +1842,91 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>500346</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>651087</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D46" s="1" t="s">
+      <x:c r="E46" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F46" s="1">
-        <x:v>1426379</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D47" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B47" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C47" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D47" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F47" s="1">
-        <x:v>566488</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1934,45 +1934,45 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1426379</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>333</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1980,114 +1980,114 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>1974</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-31053</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B52" s="1" t="s">
+      <x:c r="D52" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D52" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>-46</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>2326917</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>499160</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2095,114 +2095,114 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>663879</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
         <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>1642139</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>663879</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>500000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>382</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2210,91 +2210,91 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1870</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>2000000</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-9678</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>5734013</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2302,45 +2302,45 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>20139905</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>60000</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2348,22 +2348,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>152765</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2371,45 +2371,45 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>198972</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>253656</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2417,68 +2417,68 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>350000</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>1183678</x:v>
+        <x:v>10498736</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>108000</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2486,68 +2486,68 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1183678</x:v>
+        <x:v>651087</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>-62727</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>382</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>12</x:v>
@@ -2555,25 +2555,25 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>33653</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
@@ -2584,16 +2584,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>2651</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2601,45 +2601,45 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-6917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>149773</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2647,22 +2647,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>20304</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2670,22 +2670,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>104555</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2693,22 +2693,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>253750</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2716,22 +2716,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>104555</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2783,13 +2783,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2800,13 +2800,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2817,13 +2817,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2834,13 +2834,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2851,13 +2851,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2868,30 +2868,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2902,30 +2902,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2936,13 +2936,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2953,30 +2953,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2987,13 +2987,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3004,30 +3004,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3038,47 +3038,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3089,30 +3089,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3123,47 +3123,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3174,13 +3174,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3191,13 +3191,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3208,47 +3208,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3259,13 +3259,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3276,30 +3276,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3310,13 +3310,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10542389</x:v>
@@ -3327,13 +3327,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3344,13 +3344,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3361,30 +3361,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3395,13 +3395,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3412,13 +3412,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3429,30 +3429,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3463,13 +3463,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B42" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C42" s="1" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3480,13 +3480,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C43" s="1" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3497,13 +3497,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1217575</x:v>
@@ -3514,13 +3514,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3531,30 +3531,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3565,30 +3565,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3599,13 +3599,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>11995</x:v>
@@ -3616,30 +3616,30 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3650,13 +3650,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3667,13 +3667,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3684,30 +3684,30 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>39386</x:v>
@@ -3718,30 +3718,30 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>164138</x:v>
@@ -3752,13 +3752,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>-62727</x:v>
@@ -3769,13 +3769,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>214831</x:v>
@@ -3786,13 +3786,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>382</x:v>
@@ -3843,10 +3843,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3857,10 +3857,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3871,10 +3871,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3885,10 +3885,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3899,10 +3899,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3913,24 +3913,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3941,24 +3941,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3969,10 +3969,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3983,24 +3983,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4011,10 +4011,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4025,24 +4025,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4053,24 +4053,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4081,24 +4081,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4109,24 +4109,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4137,38 +4137,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4179,10 +4179,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4193,24 +4193,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10562693</x:v>
@@ -4221,10 +4221,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4235,10 +4235,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4249,24 +4249,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4277,10 +4277,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4291,10 +4291,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4305,24 +4305,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4333,10 +4333,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4347,10 +4347,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1219931</x:v>
@@ -4361,24 +4361,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4389,24 +4389,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4417,10 +4417,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>11995</x:v>
@@ -4431,24 +4431,24 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4459,10 +4459,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4473,10 +4473,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4487,24 +4487,24 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>39386</x:v>
@@ -4515,24 +4515,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>164138</x:v>
@@ -4543,10 +4543,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>-62727</x:v>
@@ -4557,10 +4557,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>214831</x:v>
@@ -4571,10 +4571,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>382</x:v>
@@ -4621,7 +4621,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4632,18 +4632,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4654,7 +4654,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4665,29 +4665,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4698,29 +4698,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4731,7 +4731,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4742,18 +4742,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10563075</x:v>
@@ -4764,7 +4764,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4775,18 +4775,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4797,7 +4797,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4808,18 +4808,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4830,7 +4830,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1220869</x:v>
@@ -4841,18 +4841,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4863,18 +4863,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4885,7 +4885,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4896,18 +4896,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4918,7 +4918,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4929,7 +4929,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>214831</x:v>
@@ -4940,7 +4940,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -4983,7 +4983,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4991,7 +4991,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -4999,7 +4999,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5007,7 +5007,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5015,7 +5015,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5023,7 +5023,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5031,7 +5031,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5039,7 +5039,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5047,7 +5047,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30702980</x:v>
@@ -5055,7 +5055,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5063,7 +5063,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5071,7 +5071,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5079,7 +5079,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5087,7 +5087,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1220869</x:v>
@@ -5095,7 +5095,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5103,7 +5103,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>-18676</x:v>
@@ -5111,7 +5111,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5119,7 +5119,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5127,7 +5127,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5135,7 +5135,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5143,7 +5143,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5187,10 +5187,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5198,10 +5198,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5209,10 +5209,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5220,10 +5220,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5231,10 +5231,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5242,10 +5242,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5253,10 +5253,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5264,10 +5264,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5275,10 +5275,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5286,10 +5286,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5297,10 +5297,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5308,10 +5308,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5319,10 +5319,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5341,10 +5341,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5352,10 +5352,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5363,10 +5363,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5374,10 +5374,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5385,10 +5385,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5396,10 +5396,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5407,10 +5407,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5418,10 +5418,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5429,10 +5429,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5440,10 +5440,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30638641</x:v>
@@ -5451,10 +5451,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5462,10 +5462,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5473,10 +5473,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5495,10 +5495,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5506,10 +5506,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5517,10 +5517,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1217575</x:v>
@@ -5528,10 +5528,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5539,10 +5539,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5550,10 +5550,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5561,10 +5561,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5572,10 +5572,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -5583,10 +5583,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>11995</x:v>
@@ -5594,10 +5594,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -5605,10 +5605,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>764</x:v>
@@ -5616,10 +5616,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>178402</x:v>
@@ -5627,10 +5627,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>39386</x:v>
@@ -5638,10 +5638,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -5649,10 +5649,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-62727</x:v>
@@ -5660,10 +5660,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>214831</x:v>
@@ -5671,10 +5671,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,6 +42,102 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -51,15 +147,9 @@
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>KY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
@@ -72,114 +162,24 @@
     <x:t>10</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
     <x:t>35</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
     <x:t>BIRD, SHANNON KATHLEEN</x:t>
   </x:si>
   <x:si>
@@ -288,6 +288,45 @@
     <x:t>09</x:t>
   </x:si>
   <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
@@ -322,45 +361,6 @@
   </x:si>
   <x:si>
     <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
   </x:si>
   <x:si>
     <x:t>STELSON, JANELLE</x:t>
@@ -891,7 +891,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>3515615</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -899,22 +899,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>11995</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -922,91 +922,91 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
+      <x:c r="E4" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>164138</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>4968501</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>579319</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1014,160 +1014,160 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>3515616</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>333</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>1974</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>-31053</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>-46</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>499160</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1175,85 +1175,85 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>663879</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>1642139</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>663879</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>54</x:v>
@@ -1267,19 +1267,19 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>938</x:v>
@@ -1302,7 +1302,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
         <x:v>63298</x:v>
@@ -1313,16 +1313,16 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>61</x:v>
@@ -1345,10 +1345,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F22" s="1">
         <x:v>3985698</x:v>
@@ -1359,10 +1359,10 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>65</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
         <x:v>825294</x:v>
@@ -1400,7 +1400,7 @@
         <x:v>299290</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
@@ -1414,10 +1414,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F25" s="1">
         <x:v>3985700</x:v>
@@ -1428,39 +1428,39 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>72</x:v>
@@ -1474,16 +1474,16 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>74</x:v>
@@ -1492,15 +1492,15 @@
         <x:v>1870</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>75</x:v>
@@ -1509,44 +1509,44 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F30" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>78</x:v>
@@ -1566,10 +1566,10 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>81</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
@@ -1598,10 +1598,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
         <x:v>60000</x:v>
@@ -1618,13 +1618,13 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
         <x:v>152765</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>74</x:v>
@@ -1653,24 +1653,24 @@
         <x:v>198972</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F36" s="1">
         <x:v>253656</x:v>
@@ -1681,19 +1681,19 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F37" s="1">
         <x:v>350000</x:v>
@@ -1704,10 +1704,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>87</x:v>
@@ -1716,13 +1716,13 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F38" s="1">
         <x:v>1183678</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
@@ -1733,13 +1733,13 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
         <x:v>108000</x:v>
@@ -1750,10 +1750,10 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>87</x:v>
@@ -1762,56 +1762,56 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F40" s="1">
         <x:v>1183678</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>362844</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>333</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1819,22 +1819,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>382</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1842,68 +1842,68 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>3575107</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>59748</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>-28160</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1917,16 +1917,16 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>39386</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1934,22 +1934,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>198972</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1957,22 +1957,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>4379243</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -1980,68 +1980,68 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>3232621</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>2326917</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>4379246</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2055,16 +2055,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>-62727</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2072,68 +2072,68 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>382</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>33653</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>2651</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2141,45 +2141,45 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>-6917</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>149773</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2187,22 +2187,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>20304</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2210,68 +2210,68 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>104555</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>253750</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B62" s="1" t="s">
+      <x:c r="D62" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="D62" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>104555</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2279,19 +2279,19 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F63" s="1">
         <x:v>382</x:v>
@@ -2302,10 +2302,10 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
         <x:v>78</x:v>
@@ -2325,19 +2325,19 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F65" s="1">
         <x:v>58441</x:v>
@@ -2348,10 +2348,10 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
         <x:v>115</x:v>
@@ -2360,7 +2360,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F66" s="1">
         <x:v>382</x:v>
@@ -2371,42 +2371,42 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E67" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="E67" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="F67" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>382</x:v>
@@ -2417,16 +2417,16 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
         <x:v>120</x:v>
@@ -2435,18 +2435,18 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>55</x:v>
@@ -2475,7 +2475,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F71" s="1">
         <x:v>500346</x:v>
@@ -2486,19 +2486,19 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F72" s="1">
         <x:v>651087</x:v>
@@ -2515,36 +2515,36 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F73" s="1">
         <x:v>1426379</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F74" s="1">
         <x:v>566488</x:v>
@@ -2561,30 +2561,30 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F75" s="1">
         <x:v>1426379</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
         <x:v>55</x:v>
@@ -2601,19 +2601,19 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F77" s="1">
         <x:v>382</x:v>
@@ -2624,10 +2624,10 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>123</x:v>
@@ -2647,16 +2647,16 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
         <x:v>120</x:v>
@@ -2670,16 +2670,16 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>127</x:v>
@@ -2705,7 +2705,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F81" s="1">
         <x:v>4383748</x:v>
@@ -2728,7 +2728,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F82" s="1">
         <x:v>4383749</x:v>
@@ -2783,13 +2783,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2800,13 +2800,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2823,7 +2823,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2837,10 +2837,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2857,7 +2857,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825294</x:v>
@@ -2868,30 +2868,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>108000</x:v>
@@ -2905,27 +2905,27 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2936,13 +2936,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2959,24 +2959,24 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2990,7 +2990,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>54</x:v>
@@ -3016,18 +3016,18 @@
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3041,44 +3041,44 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3089,19 +3089,19 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
@@ -3109,10 +3109,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3129,41 +3129,41 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3174,13 +3174,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3197,7 +3197,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3208,47 +3208,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3288,12 +3288,12 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>55</x:v>
@@ -3310,7 +3310,7 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>55</x:v>
@@ -3330,7 +3330,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>72</x:v>
@@ -3364,7 +3364,7 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>120</x:v>
@@ -3373,7 +3373,7 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
@@ -3381,7 +3381,7 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
         <x:v>120</x:v>
@@ -3395,7 +3395,7 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
         <x:v>55</x:v>
@@ -3415,7 +3415,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>61</x:v>
@@ -3432,7 +3432,7 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
         <x:v>74</x:v>
@@ -3441,15 +3441,15 @@
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>74</x:v>
@@ -3463,13 +3463,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3480,13 +3480,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3500,10 +3500,10 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1217575</x:v>
@@ -3517,10 +3517,10 @@
         <x:v>118</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3531,19 +3531,19 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
@@ -3551,10 +3551,10 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3565,19 +3565,19 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
@@ -3585,10 +3585,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3599,13 +3599,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>11995</x:v>
@@ -3616,19 +3616,19 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
@@ -3639,7 +3639,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3650,13 +3650,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3670,10 +3670,10 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3684,30 +3684,30 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>39386</x:v>
@@ -3721,27 +3721,27 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C57" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>164138</x:v>
@@ -3752,13 +3752,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>-62727</x:v>
@@ -3772,7 +3772,7 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>127</x:v>
@@ -3786,13 +3786,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>382</x:v>
@@ -3846,7 +3846,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3857,10 +3857,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3874,7 +3874,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3885,10 +3885,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3902,7 +3902,7 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825294</x:v>
@@ -3913,24 +3913,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642139</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>108000</x:v>
@@ -3941,24 +3941,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3969,10 +3969,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3986,13 +3986,13 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -4000,7 +4000,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4011,7 +4011,7 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>54</x:v>
@@ -4034,15 +4034,15 @@
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4053,24 +4053,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4081,24 +4081,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4112,13 +4112,13 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
@@ -4126,7 +4126,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4137,38 +4137,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4202,7 +4202,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
@@ -4221,7 +4221,7 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>72</x:v>
@@ -4249,7 +4249,7 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
         <x:v>120</x:v>
@@ -4258,12 +4258,12 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
         <x:v>120</x:v>
@@ -4291,7 +4291,7 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>61</x:v>
@@ -4305,7 +4305,7 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
         <x:v>74</x:v>
@@ -4314,12 +4314,12 @@
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>74</x:v>
@@ -4336,7 +4336,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4347,10 +4347,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1219931</x:v>
@@ -4361,24 +4361,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4389,24 +4389,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4417,10 +4417,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>11995</x:v>
@@ -4431,16 +4431,16 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
@@ -4448,7 +4448,7 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4459,10 +4459,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4473,10 +4473,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4487,24 +4487,24 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>39386</x:v>
@@ -4515,24 +4515,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B51" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>164138</x:v>
@@ -4546,7 +4546,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>-62727</x:v>
@@ -4557,7 +4557,7 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
         <x:v>127</x:v>
@@ -4571,10 +4571,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>382</x:v>
@@ -4621,7 +4621,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4632,18 +4632,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142139</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1681023</x:v>
@@ -4671,23 +4671,23 @@
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4698,29 +4698,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4748,7 +4748,7 @@
         <x:v>20139905</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
@@ -4781,7 +4781,7 @@
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
@@ -4814,7 +4814,7 @@
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
@@ -4830,7 +4830,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1220869</x:v>
@@ -4841,18 +4841,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4863,18 +4863,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4885,7 +4885,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4896,18 +4896,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4918,7 +4918,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4940,7 +4940,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -4983,7 +4983,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4991,7 +4991,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5823162</x:v>
@@ -5015,7 +5015,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5023,7 +5023,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5031,7 +5031,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5087,7 +5087,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1220869</x:v>
@@ -5095,7 +5095,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5103,7 +5103,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>-18676</x:v>
@@ -5111,7 +5111,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5119,7 +5119,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5127,7 +5127,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5143,7 +5143,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5190,7 +5190,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5198,10 +5198,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5209,10 +5209,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5223,7 +5223,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5234,7 +5234,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>168000</x:v>
@@ -5242,10 +5242,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5253,7 +5253,7 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
         <x:v>54</x:v>
@@ -5275,10 +5275,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5286,10 +5286,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5297,10 +5297,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5311,7 +5311,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5322,7 +5322,7 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5333,7 +5333,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5341,10 +5341,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5352,10 +5352,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5363,10 +5363,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5374,10 +5374,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5385,7 +5385,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
         <x:v>80</x:v>
@@ -5396,7 +5396,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>80</x:v>
@@ -5407,7 +5407,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>72</x:v>
@@ -5429,7 +5429,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
         <x:v>72</x:v>
@@ -5440,7 +5440,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
         <x:v>72</x:v>
@@ -5451,7 +5451,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
         <x:v>124</x:v>
@@ -5462,7 +5462,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>120</x:v>
@@ -5473,7 +5473,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>61</x:v>
@@ -5484,7 +5484,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>61</x:v>
@@ -5495,7 +5495,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
         <x:v>74</x:v>
@@ -5517,10 +5517,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1217575</x:v>
@@ -5528,10 +5528,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5539,10 +5539,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5550,10 +5550,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5561,10 +5561,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5572,10 +5572,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -5583,10 +5583,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>11995</x:v>
@@ -5594,10 +5594,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -5605,10 +5605,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>764</x:v>
@@ -5616,10 +5616,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>178402</x:v>
@@ -5630,7 +5630,7 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>39386</x:v>
@@ -5638,10 +5638,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -5649,10 +5649,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-62727</x:v>
@@ -5660,7 +5660,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>127</x:v>
@@ -5671,10 +5671,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,37 +42,280 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
@@ -81,165 +324,27 @@
     <x:t>16</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>HERRERA, BRANDON</x:t>
   </x:si>
   <x:si>
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>MOSS, JEREMY</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
@@ -255,78 +360,18 @@
     <x:t>COLLINS, KINA</x:t>
   </x:si>
   <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
     <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
     <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
@@ -336,9 +381,6 @@
     <x:t>COGNETTI, PAIGE</x:t>
   </x:si>
   <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
@@ -361,48 +403,6 @@
   </x:si>
   <x:si>
     <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -891,7 +891,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>333</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -899,22 +899,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1974</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -922,91 +922,91 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>-46</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>2326917</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>499160</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1014,91 +1014,91 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>663879</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>1642139</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>663879</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>3515615</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1106,22 +1106,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>11995</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1129,22 +1129,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>382</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1152,22 +1152,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>164138</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1175,22 +1175,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>4968501</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1198,22 +1198,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>579319</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1221,22 +1221,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>3515616</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1244,22 +1244,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>715</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1267,22 +1267,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>938</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1290,22 +1290,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>63298</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1313,22 +1313,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>600000</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1336,45 +1336,45 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>3985698</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>825294</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1382,45 +1382,45 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>299290</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>3985700</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1428,45 +1428,45 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>500000</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>382</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1474,91 +1474,91 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1870</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>2000000</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-9678</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>5734013</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1566,45 +1566,45 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>20139905</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>60000</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1612,22 +1612,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>152765</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1635,45 +1635,45 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>198972</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>253656</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1681,22 +1681,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>350000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1704,45 +1704,45 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1183678</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>108000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1750,45 +1750,45 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1183678</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-62727</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1796,22 +1796,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>382</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1819,22 +1819,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>33653</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1842,91 +1842,91 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>2651</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>-6917</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>149773</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>20304</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1934,22 +1934,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1957,114 +1957,114 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>253750</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>104555</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="D51" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D51" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>362844</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>333</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>382</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2072,91 +2072,91 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>3575107</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>59748</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>-28160</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>39386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2164,137 +2164,137 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>198972</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>4379243</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>3232621</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>2326917</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>4379246</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>382</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2302,22 +2302,22 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>382</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2325,22 +2325,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>58441</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2348,68 +2348,68 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>382</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>14264</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>382</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2417,91 +2417,91 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>2435149</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>10498736</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>500346</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>651087</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2509,91 +2509,91 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1426379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>566488</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>1426379</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>10000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2601,22 +2601,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2624,22 +2624,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>2649</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2647,22 +2647,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>685627</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2670,68 +2670,68 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>214831</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="E81" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F81" s="1">
-        <x:v>4383748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>4383749</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2783,13 +2783,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2800,13 +2800,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2817,13 +2817,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2834,13 +2834,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2851,16 +2851,16 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="1">
-        <x:v>825294</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
@@ -2868,33 +2868,33 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D7" s="1">
-        <x:v>1642139</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D8" s="1">
-        <x:v>108000</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>12</x:v>
@@ -2902,30 +2902,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2936,13 +2936,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2953,30 +2953,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2987,13 +2987,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3004,30 +3004,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3038,47 +3038,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3089,30 +3089,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3123,47 +3123,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3174,13 +3174,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3191,13 +3191,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3208,47 +3208,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3259,13 +3259,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3276,30 +3276,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D31" s="1">
-        <x:v>20139905</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3310,16 +3310,16 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D33" s="1">
-        <x:v>10542389</x:v>
+        <x:v>10561475</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>12</x:v>
@@ -3327,13 +3327,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3344,13 +3344,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3361,30 +3361,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3395,13 +3395,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3412,13 +3412,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C39" s="1" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3429,30 +3429,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3463,13 +3463,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3480,13 +3480,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3497,16 +3497,16 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D44" s="1">
-        <x:v>1217575</x:v>
+        <x:v>1206055</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>12</x:v>
@@ -3514,13 +3514,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3531,30 +3531,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3565,19 +3565,19 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
@@ -3585,10 +3585,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3599,13 +3599,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>11995</x:v>
@@ -3616,30 +3616,30 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>382</x:v>
@@ -3650,13 +3650,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3667,13 +3667,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3684,30 +3684,30 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>39386</x:v>
@@ -3718,30 +3718,30 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>164138</x:v>
@@ -3752,13 +3752,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>-62727</x:v>
@@ -3769,13 +3769,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>214831</x:v>
@@ -3786,13 +3786,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>382</x:v>
@@ -3843,10 +3843,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3857,10 +3857,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3871,10 +3871,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3885,10 +3885,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3899,13 +3899,13 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>825294</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>12</x:v>
@@ -3913,27 +3913,27 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="1">
-        <x:v>1642139</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1">
-        <x:v>108000</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>12</x:v>
@@ -3941,24 +3941,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3969,10 +3969,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3983,24 +3983,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4011,10 +4011,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4025,24 +4025,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4053,24 +4053,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4081,24 +4081,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4109,24 +4109,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4137,38 +4137,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4179,10 +4179,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4193,27 +4193,27 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C27" s="1">
-        <x:v>20139905</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C28" s="1">
-        <x:v>10562693</x:v>
+        <x:v>10581779</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
         <x:v>12</x:v>
@@ -4221,10 +4221,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4235,10 +4235,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4249,24 +4249,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4277,10 +4277,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4291,10 +4291,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4305,24 +4305,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4333,10 +4333,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4347,13 +4347,13 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>1219931</x:v>
+        <x:v>1208411</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
         <x:v>12</x:v>
@@ -4361,24 +4361,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4389,24 +4389,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4417,10 +4417,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>11995</x:v>
@@ -4431,24 +4431,24 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>382</x:v>
@@ -4459,10 +4459,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4473,10 +4473,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4487,24 +4487,24 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>39386</x:v>
@@ -4515,24 +4515,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>164138</x:v>
@@ -4543,10 +4543,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>-62727</x:v>
@@ -4557,10 +4557,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>214831</x:v>
@@ -4571,10 +4571,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>382</x:v>
@@ -4621,7 +4621,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4632,21 +4632,21 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>4142139</x:v>
+        <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="1">
-        <x:v>1681023</x:v>
+        <x:v>1677070</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>12</x:v>
@@ -4654,7 +4654,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4665,29 +4665,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4698,29 +4698,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4731,7 +4731,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4742,21 +4742,21 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1">
-        <x:v>20139905</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1">
-        <x:v>10563075</x:v>
+        <x:v>10582161</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>12</x:v>
@@ -4764,7 +4764,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4775,18 +4775,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4797,7 +4797,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4808,18 +4808,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4830,10 +4830,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1">
-        <x:v>1220869</x:v>
+        <x:v>1209349</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>12</x:v>
@@ -4841,18 +4841,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4863,18 +4863,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4885,7 +4885,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4896,18 +4896,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4918,7 +4918,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4929,7 +4929,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>214831</x:v>
@@ -4940,7 +4940,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -4983,7 +4983,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4991,15 +4991,15 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B3" s="1">
-        <x:v>5823162</x:v>
+        <x:v>5819210</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5007,7 +5007,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5015,7 +5015,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5023,7 +5023,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5031,7 +5031,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5039,7 +5039,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5047,15 +5047,15 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1">
-        <x:v>30702980</x:v>
+        <x:v>30723070</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5063,7 +5063,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5071,7 +5071,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5079,7 +5079,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5087,15 +5087,15 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="1">
-        <x:v>1220869</x:v>
+        <x:v>1209349</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5103,7 +5103,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>-18676</x:v>
@@ -5111,7 +5111,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5119,7 +5119,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5127,7 +5127,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5135,7 +5135,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5143,7 +5143,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5187,10 +5187,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5198,10 +5198,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5209,10 +5209,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5220,10 +5220,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5231,21 +5231,21 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1">
-        <x:v>168000</x:v>
+        <x:v>164048</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5253,10 +5253,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5264,10 +5264,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5275,10 +5275,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5286,10 +5286,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5297,10 +5297,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5308,10 +5308,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5319,10 +5319,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5341,10 +5341,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5352,10 +5352,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5363,10 +5363,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5374,10 +5374,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5385,10 +5385,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5396,10 +5396,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5407,10 +5407,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5418,10 +5418,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5429,10 +5429,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5440,21 +5440,21 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1">
-        <x:v>30638641</x:v>
+        <x:v>30658731</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5462,10 +5462,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5473,10 +5473,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5495,10 +5495,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5506,10 +5506,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5517,21 +5517,21 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C32" s="1">
-        <x:v>1217575</x:v>
+        <x:v>1206055</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5539,10 +5539,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5550,10 +5550,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5561,10 +5561,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5572,10 +5572,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>382</x:v>
@@ -5583,10 +5583,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>11995</x:v>
@@ -5594,10 +5594,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B39" s="1" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>-31053</x:v>
@@ -5605,10 +5605,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>764</x:v>
@@ -5616,10 +5616,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>178402</x:v>
@@ -5627,10 +5627,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>39386</x:v>
@@ -5638,10 +5638,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>-46</x:v>
@@ -5649,10 +5649,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-62727</x:v>
@@ -5660,10 +5660,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>214831</x:v>
@@ -5671,10 +5671,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,6 +42,96 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -57,39 +147,18 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOLDMAN, DANIEL</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
@@ -99,70 +168,94 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
   </x:si>
   <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
     <x:t>BIRD, SHANNON KATHLEEN</x:t>
@@ -183,15 +276,6 @@
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>BABB TOMLINSON, LAUREN</x:t>
   </x:si>
   <x:si>
@@ -213,9 +297,6 @@
     <x:t>FL</x:t>
   </x:si>
   <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>TRUMP, DONALD J.</x:t>
   </x:si>
   <x:si>
@@ -237,12 +318,6 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
@@ -255,12 +330,6 @@
     <x:t>AK</x:t>
   </x:si>
   <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
@@ -270,24 +339,6 @@
     <x:t>PA</x:t>
   </x:si>
   <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONLEY, CAIT</x:t>
   </x:si>
   <x:si>
@@ -306,16 +357,40 @@
     <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
@@ -330,79 +405,10 @@
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -473,8 +479,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G82" totalsRowShown="0">
-  <x:autoFilter ref="A1:G82"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G83" totalsRowShown="0">
+  <x:autoFilter ref="A1:G83"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -489,8 +495,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E61" totalsRowShown="0">
-  <x:autoFilter ref="A1:E61"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E62" totalsRowShown="0">
+  <x:autoFilter ref="A1:E62"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -503,8 +509,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D54" totalsRowShown="0">
-  <x:autoFilter ref="A1:D54"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D55" totalsRowShown="0">
+  <x:autoFilter ref="A1:D55"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -539,8 +545,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C46" totalsRowShown="0">
-  <x:autoFilter ref="A1:C46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C47" totalsRowShown="0">
+  <x:autoFilter ref="A1:C47"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -838,7 +844,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G82"/>
+  <x:dimension ref="A1:G83"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -891,7 +897,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>3515615</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -914,7 +920,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -922,22 +928,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>382</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -945,22 +951,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>164138</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -968,22 +974,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="C6" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>4968501</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -991,22 +997,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>579319</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1014,45 +1020,45 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>3515616</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>10000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1060,22 +1066,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>382</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1083,22 +1089,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>2649</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1106,22 +1112,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>685627</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1129,22 +1135,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>214831</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1152,22 +1158,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>4383748</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1175,22 +1181,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>4383749</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1198,22 +1204,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>715</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1221,45 +1227,45 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>938</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>825293</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1267,79 +1273,79 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
       <x:c r="F19" s="1">
-        <x:v>63298</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>600000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>3985698</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>61</x:v>
@@ -1351,53 +1357,53 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>299290</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3985700</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>-62727</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1405,22 +1411,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>382</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1428,22 +1434,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>33653</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1451,68 +1457,68 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>2651</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>-6917</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>149773</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1520,68 +1526,68 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>20304</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>253750</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
+      <x:c r="D32" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D32" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F32" s="1">
-        <x:v>104555</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1589,22 +1595,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>104555</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1612,22 +1618,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>382</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1635,22 +1641,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>382</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1658,22 +1664,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>58441</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1681,22 +1687,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>382</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1704,45 +1710,45 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F38" s="1">
-        <x:v>14264</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>382</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1750,45 +1756,45 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>2435149</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>10517822</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1796,22 +1802,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>500346</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1819,22 +1825,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>1046779</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1842,45 +1848,45 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>1426379</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>159276</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1888,45 +1894,45 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>1426379</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>333</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1934,22 +1940,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1974</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1957,114 +1963,114 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>1642140</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>-31053</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>2326917</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>499160</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2072,91 +2078,91 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>663879</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>663879</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>500000</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>382</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2164,91 +2170,91 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1870</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2000000</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>-9678</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>5734013</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2256,68 +2262,68 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>20140909</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>104048</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>60000</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2325,22 +2331,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>152765</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2348,68 +2354,68 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>198972</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>253656</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>350000</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2417,183 +2423,183 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>1183678</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>1183678</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>362844</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>333</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>382</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>3575107</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>59748</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2601,140 +2607,163 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>39386</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>198972</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C79" s="1" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="B79" s="1" t="s">
+      <x:c r="D79" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="C79" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D79" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>4379243</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>2326917</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>4379246</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:7">
+      <x:c r="A83" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F83" s="1">
+        <x:v>663879</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2753,7 +2782,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E61"/>
+  <x:dimension ref="A1:E62"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2783,13 +2812,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2800,13 +2829,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2817,13 +2846,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2834,13 +2863,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2851,13 +2880,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825293</x:v>
@@ -2868,30 +2897,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>104048</x:v>
@@ -2902,30 +2931,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2936,13 +2965,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2953,30 +2982,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -2987,13 +3016,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3004,30 +3033,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3038,47 +3067,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3089,30 +3118,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3123,47 +3152,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3174,13 +3203,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3191,13 +3220,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3208,47 +3237,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3259,13 +3288,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3276,30 +3305,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3310,13 +3339,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3327,13 +3356,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3344,13 +3373,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3361,30 +3390,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3395,13 +3424,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3412,13 +3441,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3429,30 +3458,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3463,13 +3492,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3480,13 +3509,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3497,13 +3526,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1206055</x:v>
@@ -3514,13 +3543,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3531,30 +3560,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3565,30 +3594,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3599,64 +3628,64 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D50" s="1">
-        <x:v>11995</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D51" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D52" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3667,13 +3696,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3684,84 +3713,84 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D56" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D57" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D58" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D59" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
         <x:v>12</x:v>
@@ -3769,16 +3798,16 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D60" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>12</x:v>
@@ -3786,18 +3815,35 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D61" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="E61" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:5">
+      <x:c r="A62" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D62" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E61" s="1" t="s">
+      <x:c r="E62" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3817,7 +3863,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D54"/>
+  <x:dimension ref="A1:D55"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3843,10 +3889,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3857,10 +3903,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3871,10 +3917,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3885,10 +3931,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3899,10 +3945,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825293</x:v>
@@ -3913,24 +3959,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>104048</x:v>
@@ -3941,24 +3987,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -3969,10 +4015,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -3983,24 +4029,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4011,10 +4057,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4025,24 +4071,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4053,24 +4099,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4081,24 +4127,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4109,24 +4155,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4137,38 +4183,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4179,10 +4225,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4193,24 +4239,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4221,10 +4267,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4235,10 +4281,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4249,24 +4295,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4277,10 +4323,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4291,10 +4337,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4305,24 +4351,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4333,10 +4379,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4347,10 +4393,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1208411</x:v>
@@ -4361,24 +4407,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4389,24 +4435,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4417,52 +4463,52 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>11995</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>382</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4476,7 +4522,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4487,69 +4533,69 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
         <x:v>12</x:v>
@@ -4557,13 +4603,13 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>12</x:v>
@@ -4571,15 +4617,29 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C54" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C55" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D54" s="1" t="s">
+      <x:c r="D55" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4621,7 +4681,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4632,18 +4692,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1677070</x:v>
@@ -4654,7 +4714,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4665,29 +4725,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4698,29 +4758,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4731,7 +4791,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4742,18 +4802,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4764,7 +4824,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4775,18 +4835,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4797,7 +4857,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4808,18 +4868,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4830,7 +4890,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1209349</x:v>
@@ -4841,18 +4901,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4863,18 +4923,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B24" s="1">
-        <x:v>-31053</x:v>
+        <x:v>307355</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4885,7 +4945,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4896,18 +4956,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4918,7 +4978,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4929,7 +4989,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>214831</x:v>
@@ -4940,7 +5000,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -4983,7 +5043,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4991,7 +5051,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5819210</x:v>
@@ -4999,7 +5059,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5007,7 +5067,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5015,7 +5075,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5023,7 +5083,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5031,7 +5091,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5039,7 +5099,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5047,7 +5107,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5055,7 +5115,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5063,7 +5123,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5071,7 +5131,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5079,7 +5139,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5087,7 +5147,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1209349</x:v>
@@ -5095,7 +5155,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5103,15 +5163,15 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1">
-        <x:v>-18676</x:v>
+        <x:v>319732</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5119,7 +5179,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5127,7 +5187,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5135,7 +5195,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5143,7 +5203,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5165,7 +5225,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C46"/>
+  <x:dimension ref="A1:C47"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5187,10 +5247,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5198,10 +5258,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5209,10 +5269,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5220,10 +5280,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5231,10 +5291,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>164048</x:v>
@@ -5242,10 +5302,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5253,10 +5313,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5264,10 +5324,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5275,10 +5335,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5286,10 +5346,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5297,10 +5357,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5308,10 +5368,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5319,10 +5379,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5330,10 +5390,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5341,10 +5401,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5352,10 +5412,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5363,10 +5423,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5374,10 +5434,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5385,10 +5445,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5396,10 +5456,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5407,10 +5467,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5418,10 +5478,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5429,10 +5489,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5440,10 +5500,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5451,10 +5511,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5462,10 +5522,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5473,10 +5533,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5484,10 +5544,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5495,10 +5555,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5506,10 +5566,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5517,10 +5577,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1206055</x:v>
@@ -5528,10 +5588,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5539,10 +5599,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5550,10 +5610,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5561,10 +5621,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5572,13 +5632,13 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="1">
-        <x:v>382</x:v>
+        <x:v>338408</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:3">
@@ -5586,97 +5646,108 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C38" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" s="1">
-        <x:v>-31053</x:v>
+        <x:v>11995</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C40" s="1">
-        <x:v>764</x:v>
+        <x:v>-31053</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="1">
-        <x:v>178402</x:v>
+        <x:v>764</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C46" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:3">
+      <x:c r="A47" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C47" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,37 +42,289 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>MI</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
     <x:t>CRAIG, ANGIE</x:t>
@@ -81,258 +333,27 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>MO</x:t>
   </x:si>
   <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCADAMS, BEN</x:t>
   </x:si>
   <x:si>
     <x:t>UT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>LIPETRI, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STELSON, JANELLE</x:t>
   </x:si>
   <x:si>
@@ -388,27 +409,6 @@
   </x:si>
   <x:si>
     <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -897,7 +897,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>10000</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -905,22 +905,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -928,163 +928,163 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>2649</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>685627</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>214831</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>4383748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>338408</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>4383749</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>3515615</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
@@ -1095,16 +1095,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>11995</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1112,22 +1112,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>382</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1135,22 +1135,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>164138</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1158,22 +1158,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>4968501</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1181,22 +1181,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>579319</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1204,22 +1204,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F16" s="1">
-        <x:v>3515616</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1227,45 +1227,45 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>500000</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>382</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1273,91 +1273,91 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>1870</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>2000000</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>-9678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>5734013</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1365,45 +1365,45 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>20140909</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>104048</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1411,22 +1411,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>60000</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1434,22 +1434,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>152765</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1457,45 +1457,45 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>198972</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>253656</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1503,22 +1503,22 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>350000</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1526,68 +1526,68 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
+      <x:c r="D30" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>1183678</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>1183678</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>715</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1595,22 +1595,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>938</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1618,22 +1618,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>825293</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1641,22 +1641,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>63298</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1664,45 +1664,45 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>600000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>3985698</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1710,91 +1710,91 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="F38" s="1">
-        <x:v>299290</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>3985700</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>382</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1802,45 +1802,45 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>33653</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>2651</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1848,45 +1848,45 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>-6917</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>149773</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1894,45 +1894,45 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>20304</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>253750</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1940,22 +1940,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1963,68 +1963,68 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>104555</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>382</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2032,22 +2032,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2055,22 +2055,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>382</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2078,45 +2078,45 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>14264</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C55" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D55" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>382</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2124,68 +2124,68 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>2435149</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>10517822</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>500346</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2193,22 +2193,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1046779</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2216,45 +2216,45 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1426379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>159276</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2262,68 +2262,68 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>1426379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>362844</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D64" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C64" s="1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D64" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>333</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2331,91 +2331,91 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="C65" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>16</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>382</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>3575107</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>59748</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2423,45 +2423,45 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>39386</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>198972</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2469,91 +2469,91 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>4379243</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>3232621</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>2326917</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="B74" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="C74" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>4379246</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>12</x:v>
@@ -2561,209 +2561,209 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>333</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>1974</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>1642140</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-31053</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>-46</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>2326917</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>499160</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>663879</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>663879</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2812,13 +2812,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2829,13 +2829,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2846,13 +2846,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2863,13 +2863,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2880,13 +2880,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825293</x:v>
@@ -2897,30 +2897,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>104048</x:v>
@@ -2931,30 +2931,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2965,13 +2965,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2982,30 +2982,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -3016,13 +3016,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3033,30 +3033,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3067,47 +3067,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3118,30 +3118,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3152,47 +3152,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3203,13 +3203,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3220,13 +3220,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3237,47 +3237,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3288,13 +3288,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3305,30 +3305,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3339,13 +3339,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3356,13 +3356,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3373,13 +3373,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3390,30 +3390,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3424,13 +3424,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3441,13 +3441,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3458,30 +3458,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3492,13 +3492,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3509,13 +3509,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3526,13 +3526,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1206055</x:v>
@@ -3543,13 +3543,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3560,30 +3560,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3594,30 +3594,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3628,30 +3628,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>11995</x:v>
@@ -3662,30 +3662,30 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3696,13 +3696,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>382</x:v>
@@ -3713,13 +3713,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>382</x:v>
@@ -3730,30 +3730,30 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>39386</x:v>
@@ -3764,30 +3764,30 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>164138</x:v>
@@ -3798,13 +3798,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>-62727</x:v>
@@ -3815,13 +3815,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>214831</x:v>
@@ -3832,13 +3832,13 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>382</x:v>
@@ -3889,10 +3889,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3903,10 +3903,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3917,10 +3917,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3931,10 +3931,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3945,10 +3945,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825293</x:v>
@@ -3959,24 +3959,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>104048</x:v>
@@ -3987,24 +3987,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -4015,10 +4015,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -4029,24 +4029,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4057,10 +4057,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4071,24 +4071,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4099,24 +4099,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4127,24 +4127,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4155,24 +4155,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4183,38 +4183,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4225,10 +4225,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4239,24 +4239,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4267,10 +4267,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4281,10 +4281,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4295,24 +4295,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4323,10 +4323,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4337,10 +4337,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4351,24 +4351,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4379,10 +4379,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4393,10 +4393,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1208411</x:v>
@@ -4407,24 +4407,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4435,24 +4435,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4463,24 +4463,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>11995</x:v>
@@ -4491,24 +4491,24 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4519,10 +4519,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>
@@ -4533,10 +4533,10 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>382</x:v>
@@ -4547,24 +4547,24 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>39386</x:v>
@@ -4575,24 +4575,24 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>164138</x:v>
@@ -4603,10 +4603,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>-62727</x:v>
@@ -4617,10 +4617,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>214831</x:v>
@@ -4631,10 +4631,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>382</x:v>
@@ -4681,7 +4681,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4692,18 +4692,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1677070</x:v>
@@ -4714,7 +4714,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4725,29 +4725,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4758,29 +4758,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4791,7 +4791,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4802,18 +4802,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4824,7 +4824,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4835,18 +4835,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4857,7 +4857,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4868,18 +4868,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4890,7 +4890,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1209349</x:v>
@@ -4901,18 +4901,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4923,18 +4923,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>307355</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4945,7 +4945,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>764</x:v>
@@ -4956,18 +4956,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>203524</x:v>
@@ -4978,7 +4978,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>-62727</x:v>
@@ -4989,7 +4989,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>214831</x:v>
@@ -5000,7 +5000,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>382</x:v>
@@ -5043,7 +5043,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5051,7 +5051,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5819210</x:v>
@@ -5059,7 +5059,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5067,7 +5067,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5075,7 +5075,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5083,7 +5083,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5091,7 +5091,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5099,7 +5099,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5107,7 +5107,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5115,7 +5115,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5123,7 +5123,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5131,7 +5131,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5139,7 +5139,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5147,7 +5147,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1209349</x:v>
@@ -5155,7 +5155,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5163,7 +5163,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>319732</x:v>
@@ -5171,7 +5171,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>764</x:v>
@@ -5179,7 +5179,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5187,7 +5187,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5195,7 +5195,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5203,7 +5203,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5247,10 +5247,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5258,10 +5258,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5269,10 +5269,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5280,10 +5280,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5291,10 +5291,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>164048</x:v>
@@ -5302,10 +5302,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5313,10 +5313,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5324,10 +5324,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5335,10 +5335,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5346,10 +5346,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5357,10 +5357,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5368,10 +5368,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5379,10 +5379,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5390,10 +5390,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5401,10 +5401,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5412,10 +5412,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5423,10 +5423,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5434,10 +5434,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5445,10 +5445,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5456,10 +5456,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5467,10 +5467,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5478,10 +5478,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5489,10 +5489,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5500,10 +5500,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5511,10 +5511,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5522,10 +5522,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5533,10 +5533,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5544,10 +5544,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5555,10 +5555,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5566,10 +5566,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5577,10 +5577,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1206055</x:v>
@@ -5588,10 +5588,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5599,10 +5599,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5610,10 +5610,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5621,10 +5621,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5632,10 +5632,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>338408</x:v>
@@ -5643,10 +5643,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>382</x:v>
@@ -5654,10 +5654,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>11995</x:v>
@@ -5665,10 +5665,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>-31053</x:v>
@@ -5676,10 +5676,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>764</x:v>
@@ -5687,10 +5687,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>178402</x:v>
@@ -5698,10 +5698,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>39386</x:v>
@@ -5709,10 +5709,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>-46</x:v>
@@ -5720,10 +5720,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-62727</x:v>
@@ -5731,10 +5731,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>214831</x:v>
@@ -5742,10 +5742,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,193 +42,307 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
     <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
   </x:si>
   <x:si>
     <x:t>PAPPAS, CHRIS</x:t>
   </x:si>
   <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
     <x:t>01</x:t>
   </x:si>
   <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
   </x:si>
   <x:si>
     <x:t>16</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
     <x:t>HERRERA, BRANDON</x:t>
   </x:si>
   <x:si>
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
     <x:t>AHMED, JUNAID</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
     <x:t>TRUMP, DONALD J.</x:t>
@@ -243,12 +357,6 @@
     <x:t>VA</x:t>
   </x:si>
   <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>COOPER, ROY</x:t>
   </x:si>
   <x:si>
@@ -258,18 +366,6 @@
     <x:t>IN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCMORROW, MALLORY</x:t>
   </x:si>
   <x:si>
@@ -282,100 +378,7 @@
     <x:t>AMIWALA, BUSHRA</x:t>
   </x:si>
   <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIPETRI, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
+    <x:t>BRESNAHAN, ROB</x:t>
   </x:si>
   <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
@@ -479,8 +482,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G83" totalsRowShown="0">
-  <x:autoFilter ref="A1:G83"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G84" totalsRowShown="0">
+  <x:autoFilter ref="A1:G84"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -495,8 +498,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E62" totalsRowShown="0">
-  <x:autoFilter ref="A1:E62"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E63" totalsRowShown="0">
+  <x:autoFilter ref="A1:E63"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -509,8 +512,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D55" totalsRowShown="0">
-  <x:autoFilter ref="A1:D55"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D56" totalsRowShown="0">
+  <x:autoFilter ref="A1:D56"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -522,8 +525,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C31" totalsRowShown="0">
-  <x:autoFilter ref="A1:C31"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C32" totalsRowShown="0">
+  <x:autoFilter ref="A1:C32"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -545,8 +548,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C47" totalsRowShown="0">
-  <x:autoFilter ref="A1:C47"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C48" totalsRowShown="0">
+  <x:autoFilter ref="A1:C48"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -844,7 +847,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G83"/>
+  <x:dimension ref="A1:G84"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -897,7 +900,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>333</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -905,22 +908,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>1974</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -928,114 +931,114 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>1642140</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>-31053</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>-46</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>2326917</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>499160</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1043,137 +1046,137 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>663879</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>663879</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>715</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>938</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>825293</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F14" s="1">
-        <x:v>63298</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1181,45 +1184,45 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>600000</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>3985698</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1227,45 +1230,45 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>299290</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>3985700</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1273,45 +1276,45 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>3515615</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>11995</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1319,22 +1322,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>382</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1342,68 +1345,68 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>164138</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>4968501</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>579319</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1411,22 +1414,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>3515616</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1434,22 +1437,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>-62727</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1457,22 +1460,22 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>382</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1480,22 +1483,22 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="F28" s="1">
-        <x:v>33653</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1503,22 +1506,22 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>2651</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1526,45 +1529,45 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-6917</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>149773</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1572,22 +1575,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>20304</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1595,22 +1598,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>253750</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1618,183 +1621,183 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>104555</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>104555</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>500000</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>382</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1870</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>2000000</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>-9678</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>5734013</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1802,45 +1805,45 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>20140909</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>104048</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1848,22 +1851,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>60000</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1871,22 +1874,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>152765</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1894,68 +1897,68 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>198972</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>253656</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>350000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1963,68 +1966,68 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>10000</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2032,19 +2035,19 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F52" s="1">
         <x:v>382</x:v>
@@ -2055,45 +2058,45 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>2649</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>685627</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2101,45 +2104,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>214831</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>4383748</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2147,45 +2150,45 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>338408</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2193,45 +2196,45 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>382</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>382</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2239,25 +2242,25 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>58441</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
@@ -2268,16 +2271,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>382</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2285,45 +2288,45 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>14264</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>382</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2331,68 +2334,68 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2435149</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>10517822</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>500346</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2400,22 +2403,22 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>1046779</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2423,45 +2426,45 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>1426379</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>159276</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2469,48 +2472,48 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>1426379</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>362844</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
@@ -2524,36 +2527,36 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>333</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>382</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>12</x:v>
@@ -2561,91 +2564,91 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>3575107</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>59748</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>-28160</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>39386</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2653,22 +2656,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="D79" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="D79" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>198972</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2676,22 +2679,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B80" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C80" s="1" t="s">
         <x:v>128</x:v>
       </x:c>
-      <x:c r="B80" s="1" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="C80" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>4379243</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2699,70 +2702,93 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>3232621</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F83" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:7">
+      <x:c r="A84" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="C83" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F83" s="1">
+      <x:c r="B84" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C84" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E84" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F84" s="1">
         <x:v>4379246</x:v>
       </x:c>
-      <x:c r="G83" s="1" t="s">
+      <x:c r="G84" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -2782,7 +2808,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E62"/>
+  <x:dimension ref="A1:E63"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2812,13 +2838,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2829,13 +2855,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2846,13 +2872,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2863,13 +2889,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2880,13 +2906,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825293</x:v>
@@ -2897,30 +2923,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>104048</x:v>
@@ -2931,30 +2957,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2965,13 +2991,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -2982,30 +3008,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -3016,13 +3042,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3033,30 +3059,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3067,47 +3093,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3118,30 +3144,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3152,47 +3178,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3203,13 +3229,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3220,13 +3246,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3237,47 +3263,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3288,13 +3314,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3305,30 +3331,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3339,13 +3365,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3356,13 +3382,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3373,13 +3399,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3390,30 +3416,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3424,13 +3450,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3441,13 +3467,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3458,30 +3484,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3492,13 +3518,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3509,13 +3535,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3526,13 +3552,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1206055</x:v>
@@ -3543,13 +3569,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3560,30 +3586,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3594,30 +3620,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3628,30 +3654,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>11995</x:v>
@@ -3662,30 +3688,30 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3696,30 +3722,30 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D54" s="1">
-        <x:v>382</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>382</x:v>
@@ -3730,84 +3756,84 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D56" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D57" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D58" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D59" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D60" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
         <x:v>12</x:v>
@@ -3815,16 +3841,16 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D61" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>12</x:v>
@@ -3832,18 +3858,35 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D62" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="E62" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:5">
+      <x:c r="A63" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D63" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E62" s="1" t="s">
+      <x:c r="E63" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3863,7 +3906,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D55"/>
+  <x:dimension ref="A1:D56"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3889,10 +3932,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3903,10 +3946,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3917,10 +3960,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3931,10 +3974,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3945,10 +3988,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825293</x:v>
@@ -3959,24 +4002,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>104048</x:v>
@@ -3987,24 +4030,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -4015,10 +4058,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -4029,24 +4072,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4057,10 +4100,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4071,24 +4114,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4099,24 +4142,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4127,24 +4170,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4155,24 +4198,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4183,38 +4226,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4225,10 +4268,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4239,24 +4282,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4267,10 +4310,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4281,10 +4324,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4295,24 +4338,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4323,10 +4366,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4337,10 +4380,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4351,24 +4394,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4379,10 +4422,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4393,10 +4436,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1208411</x:v>
@@ -4407,24 +4450,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4435,24 +4478,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4463,24 +4506,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>11995</x:v>
@@ -4491,24 +4534,24 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4519,24 +4562,24 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>382</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>382</x:v>
@@ -4547,69 +4590,69 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C49" s="1">
-        <x:v>-46</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C50" s="1">
-        <x:v>39386</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C51" s="1">
-        <x:v>14264</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
         <x:v>12</x:v>
@@ -4617,13 +4660,13 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C54" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>12</x:v>
@@ -4631,15 +4674,29 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C55" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C56" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D55" s="1" t="s">
+      <x:c r="D56" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4659,7 +4716,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C31"/>
+  <x:dimension ref="A1:C32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4681,7 +4738,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4692,18 +4749,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1677070</x:v>
@@ -4714,7 +4771,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4725,29 +4782,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4758,29 +4815,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4791,7 +4848,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4802,18 +4859,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4824,7 +4881,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4835,18 +4892,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4857,7 +4914,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4868,18 +4925,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4890,7 +4947,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1209349</x:v>
@@ -4901,18 +4958,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4923,18 +4980,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>307355</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -4945,43 +5002,43 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B26" s="1">
-        <x:v>764</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B27" s="1">
-        <x:v>14218</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1">
-        <x:v>203524</x:v>
+        <x:v>14218</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>-62727</x:v>
+        <x:v>203524</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>12</x:v>
@@ -4989,10 +5046,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B30" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>12</x:v>
@@ -5000,12 +5057,23 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B31" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:3">
+      <x:c r="A32" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B32" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="C32" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -5043,7 +5111,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5051,7 +5119,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5819210</x:v>
@@ -5059,7 +5127,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5067,7 +5135,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5075,7 +5143,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5083,7 +5151,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5091,7 +5159,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5099,7 +5167,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5107,7 +5175,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5115,7 +5183,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5123,7 +5191,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5131,7 +5199,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5139,7 +5207,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5147,7 +5215,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1209349</x:v>
@@ -5155,7 +5223,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5163,7 +5231,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>319732</x:v>
@@ -5171,15 +5239,15 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B18" s="1">
-        <x:v>764</x:v>
+        <x:v>250078</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5187,7 +5255,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5195,7 +5263,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5203,7 +5271,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>382</x:v>
@@ -5225,7 +5293,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C47"/>
+  <x:dimension ref="A1:C48"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5247,10 +5315,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5258,10 +5326,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5269,10 +5337,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5280,10 +5348,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5291,10 +5359,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>164048</x:v>
@@ -5302,10 +5370,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5313,10 +5381,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5324,10 +5392,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5335,10 +5403,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5346,10 +5414,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5357,10 +5425,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5368,10 +5436,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5379,10 +5447,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5390,10 +5458,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5401,10 +5469,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5412,10 +5480,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5423,10 +5491,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5434,10 +5502,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5445,10 +5513,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5456,10 +5524,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5467,10 +5535,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5478,10 +5546,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5489,10 +5557,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5500,10 +5568,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5511,10 +5579,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5522,10 +5590,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5533,10 +5601,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5544,10 +5612,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5555,10 +5623,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5566,10 +5634,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5577,10 +5645,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1206055</x:v>
@@ -5588,10 +5656,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5599,10 +5667,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5610,10 +5678,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5621,10 +5689,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5632,10 +5700,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>338408</x:v>
@@ -5643,10 +5711,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>382</x:v>
@@ -5654,10 +5722,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>11995</x:v>
@@ -5665,10 +5733,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B40" s="1" t="s">
-        <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>-31053</x:v>
@@ -5676,10 +5744,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>764</x:v>
@@ -5687,67 +5755,78 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C42" s="1">
-        <x:v>178402</x:v>
+        <x:v>249314</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:3">
+      <x:c r="A48" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="C48" s="1">
         <x:v>382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,6 +42,96 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -57,39 +147,18 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOLDMAN, DANIEL</x:t>
   </x:si>
   <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
     <x:t>02</x:t>
   </x:si>
   <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
@@ -99,39 +168,72 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>07</x:t>
   </x:si>
   <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
     <x:t>VILLEGAS, RANDY</x:t>
   </x:si>
   <x:si>
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOSS, JEREMY</x:t>
   </x:si>
   <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
     <x:t>CAVANAUGH, JOHN</x:t>
   </x:si>
   <x:si>
@@ -159,9 +261,6 @@
     <x:t>EL-SAYED, ABDUL</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
@@ -177,21 +276,9 @@
     <x:t>WIENER, SCOTT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>BAINS, JASMEET</x:t>
   </x:si>
   <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>BENNETT, REBECCA</x:t>
   </x:si>
   <x:si>
@@ -210,61 +297,106 @@
     <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
   </x:si>
   <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRESNAHAN, ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIGGANS, JENNIFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
     <x:t>BOWMAN, JAMAAL</x:t>
@@ -279,139 +411,10 @@
     <x:t>23</x:t>
   </x:si>
   <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
   </x:si>
   <x:si>
     <x:t>AHMED, JUNAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIPETRI, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRESNAHAN, ROB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -482,8 +485,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G84" totalsRowShown="0">
-  <x:autoFilter ref="A1:G84"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G85" totalsRowShown="0">
+  <x:autoFilter ref="A1:G85"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -498,8 +501,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E63" totalsRowShown="0">
-  <x:autoFilter ref="A1:E63"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E64" totalsRowShown="0">
+  <x:autoFilter ref="A1:E64"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -512,8 +515,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D56" totalsRowShown="0">
-  <x:autoFilter ref="A1:D56"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D57" totalsRowShown="0">
+  <x:autoFilter ref="A1:D57"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -525,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C32" totalsRowShown="0">
-  <x:autoFilter ref="A1:C32"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C33" totalsRowShown="0">
+  <x:autoFilter ref="A1:C33"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -847,7 +850,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G84"/>
+  <x:dimension ref="A1:G85"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -900,7 +903,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>3515615</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -923,7 +926,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>11995</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -931,22 +934,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
+      <x:c r="D4" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F4" s="1">
-        <x:v>382</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -954,22 +957,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>164138</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -977,22 +980,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="C6" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>4968501</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1000,22 +1003,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>579319</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1023,68 +1026,68 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>3515616</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>500000</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>382</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1092,91 +1095,91 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1870</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>2000000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>-9678</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>5734013</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1184,45 +1187,45 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>20140909</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>104048</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1230,22 +1233,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>60000</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1253,22 +1256,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F18" s="1">
-        <x:v>152765</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1276,45 +1279,45 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>198972</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="F20" s="1">
-        <x:v>253656</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1322,22 +1325,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>350000</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1345,68 +1348,68 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>1183678</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>1183678</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>715</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1414,33 +1417,33 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>938</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>69</x:v>
@@ -1449,10 +1452,10 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>825293</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1460,137 +1463,137 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F27" s="1">
-        <x:v>63298</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>600000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>3985698</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>299290</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>3985700</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>333</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1598,22 +1601,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>1974</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1621,163 +1624,163 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>1642140</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>-31053</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>-46</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B37" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>2326917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>499160</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>663879</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>663879</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
@@ -1788,16 +1791,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>10000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1805,22 +1808,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>382</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1828,22 +1831,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>2649</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1851,45 +1854,45 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>685627</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>214831</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1897,22 +1900,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>4383748</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1920,45 +1923,45 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>338408</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>4383749</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1966,45 +1969,45 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>382</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>382</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2012,22 +2015,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2035,19 +2038,19 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F52" s="1">
         <x:v>382</x:v>
@@ -2058,42 +2061,42 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>14264</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F54" s="1">
         <x:v>382</x:v>
@@ -2104,45 +2107,45 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>2435149</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>10517822</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2150,45 +2153,45 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>500346</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>1046779</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2196,45 +2199,45 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>1426379</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>159276</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2242,68 +2245,68 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F61" s="1">
         <x:v>1426379</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>-62727</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>382</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2311,91 +2314,91 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>33653</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>2651</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>-6917</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>149773</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2403,68 +2406,68 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>20304</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>253750</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>104555</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2472,45 +2475,45 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>249314</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>104555</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2518,137 +2521,137 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>362844</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>333</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>382</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>3575107</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>59748</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>-28160</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2656,140 +2659,163 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>39386</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>198972</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B81" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C81" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="B81" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C81" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>4379243</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B83" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B83" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>2326917</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>4379246</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:7">
+      <x:c r="A85" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B85" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="C85" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E85" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F85" s="1">
+        <x:v>663879</x:v>
+      </x:c>
+      <x:c r="G85" s="1" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2808,7 +2834,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E63"/>
+  <x:dimension ref="A1:E64"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2838,13 +2864,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2855,13 +2881,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2872,13 +2898,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2889,13 +2915,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2906,13 +2932,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825293</x:v>
@@ -2923,30 +2949,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>104048</x:v>
@@ -2957,30 +2983,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -2991,13 +3017,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -3008,30 +3034,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -3042,13 +3068,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3059,30 +3085,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3093,47 +3119,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3144,30 +3170,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3178,47 +3204,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3229,13 +3255,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3246,13 +3272,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3263,47 +3289,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3314,13 +3340,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3331,30 +3357,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3365,13 +3391,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3382,13 +3408,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3399,13 +3425,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3416,30 +3442,30 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3450,13 +3476,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3467,13 +3493,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3484,30 +3510,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3518,13 +3544,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3535,13 +3561,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3552,13 +3578,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1206055</x:v>
@@ -3569,13 +3595,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3586,30 +3612,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3620,30 +3646,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3654,30 +3680,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>11995</x:v>
@@ -3688,30 +3714,30 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3722,30 +3748,30 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>382</x:v>
@@ -3756,13 +3782,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>382</x:v>
@@ -3773,30 +3799,30 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>39386</x:v>
@@ -3807,30 +3833,30 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>164138</x:v>
@@ -3841,13 +3867,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>-62727</x:v>
@@ -3858,13 +3884,13 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>214831</x:v>
@@ -3875,18 +3901,35 @@
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D63" s="1">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="E63" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:5">
+      <x:c r="A64" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D64" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E63" s="1" t="s">
+      <x:c r="E64" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3906,7 +3949,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D56"/>
+  <x:dimension ref="A1:D57"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3932,10 +3975,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3946,10 +3989,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -3960,10 +4003,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -3974,10 +4017,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -3988,10 +4031,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825293</x:v>
@@ -4002,24 +4045,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>104048</x:v>
@@ -4030,24 +4073,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -4058,10 +4101,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -4072,24 +4115,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4100,10 +4143,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4114,24 +4157,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4142,24 +4185,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4170,24 +4213,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4198,24 +4241,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4226,38 +4269,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4268,10 +4311,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4282,24 +4325,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4310,10 +4353,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4324,10 +4367,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4338,24 +4381,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4366,10 +4409,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4380,10 +4423,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4394,24 +4437,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4422,10 +4465,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4436,10 +4479,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1208411</x:v>
@@ -4450,24 +4493,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4478,24 +4521,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4506,24 +4549,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>11995</x:v>
@@ -4534,24 +4577,24 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4562,24 +4605,24 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>382</x:v>
@@ -4590,10 +4633,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>382</x:v>
@@ -4604,24 +4647,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>39386</x:v>
@@ -4632,24 +4675,24 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>14264</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>164138</x:v>
@@ -4660,10 +4703,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>-62727</x:v>
@@ -4674,10 +4717,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>214831</x:v>
@@ -4688,15 +4731,29 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C56" s="1">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="1" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C57" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D56" s="1" t="s">
+      <x:c r="D57" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4716,7 +4773,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C32"/>
+  <x:dimension ref="A1:C33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -4738,7 +4795,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4749,18 +4806,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1677070</x:v>
@@ -4771,7 +4828,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4782,29 +4839,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4815,29 +4872,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4848,7 +4905,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4859,18 +4916,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4881,7 +4938,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4892,18 +4949,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4914,7 +4971,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -4925,18 +4982,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -4947,7 +5004,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1209349</x:v>
@@ -4958,18 +5015,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -4980,18 +5037,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>307355</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -5002,18 +5059,18 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>764</x:v>
@@ -5024,18 +5081,18 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>203524</x:v>
@@ -5046,7 +5103,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>-62727</x:v>
@@ -5057,7 +5114,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>214831</x:v>
@@ -5068,12 +5125,23 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B32" s="1">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:3">
+      <x:c r="A33" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B33" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
+      <x:c r="C33" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -5111,7 +5179,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5119,7 +5187,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5819210</x:v>
@@ -5127,7 +5195,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5135,7 +5203,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5143,7 +5211,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5151,7 +5219,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5159,7 +5227,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5167,7 +5235,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5175,7 +5243,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5183,7 +5251,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5191,7 +5259,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5199,7 +5267,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5207,7 +5275,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5215,7 +5283,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1209349</x:v>
@@ -5223,7 +5291,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5231,7 +5299,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>319732</x:v>
@@ -5239,7 +5307,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>250078</x:v>
@@ -5247,7 +5315,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>217742</x:v>
@@ -5255,7 +5323,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5263,7 +5331,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5271,10 +5339,10 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
-        <x:v>382</x:v>
+        <x:v>900382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5315,10 +5383,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5326,10 +5394,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5337,10 +5405,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5348,10 +5416,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5359,10 +5427,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>164048</x:v>
@@ -5370,10 +5438,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5381,10 +5449,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5392,10 +5460,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5403,10 +5471,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5414,10 +5482,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5425,10 +5493,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5436,10 +5504,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5447,10 +5515,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5458,10 +5526,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5469,10 +5537,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5480,10 +5548,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5491,10 +5559,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5502,10 +5570,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5513,10 +5581,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5524,10 +5592,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5535,10 +5603,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5546,10 +5614,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5557,10 +5625,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5568,10 +5636,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5579,10 +5647,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5590,10 +5658,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5601,10 +5669,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5612,10 +5680,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5623,10 +5691,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5634,10 +5702,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5645,10 +5713,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1206055</x:v>
@@ -5656,10 +5724,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5667,10 +5735,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5678,10 +5746,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5689,10 +5757,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5700,10 +5768,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>338408</x:v>
@@ -5711,10 +5779,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>382</x:v>
@@ -5722,10 +5790,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>11995</x:v>
@@ -5733,10 +5801,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>-31053</x:v>
@@ -5744,10 +5812,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>764</x:v>
@@ -5755,10 +5823,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>249314</x:v>
@@ -5766,10 +5834,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>178402</x:v>
@@ -5777,10 +5845,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B44" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>39386</x:v>
@@ -5788,10 +5856,10 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-46</x:v>
@@ -5799,10 +5867,10 @@
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>-62727</x:v>
@@ -5810,10 +5878,10 @@
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>214831</x:v>
@@ -5821,13 +5889,13 @@
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C48" s="1">
-        <x:v>382</x:v>
+        <x:v>900382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -42,37 +42,331 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAINS, JASMEET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAPPAS, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAHAB, AISHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOWMAN, JAMAAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERRERA, BRANDON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AHMED, JUNAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00684969</x:t>
   </x:si>
   <x:si>
     <x:t>JDCA PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRESNAHAN, ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GONZALEZ, VICENTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIGGANS, JENNIFER</x:t>
   </x:si>
   <x:si>
     <x:t>CRAIG, ANGIE</x:t>
@@ -81,288 +375,21 @@
     <x:t>MN</x:t>
   </x:si>
   <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
-  </x:si>
-  <x:si>
     <x:t>BELL, WESLEY</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCADAMS, BEN</x:t>
   </x:si>
   <x:si>
     <x:t>UT</x:t>
   </x:si>
   <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
     <x:t>LIPETRI, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAPPAS, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAINS, JASMEET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935809</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CHICAGO PROGRESSIVE PARTNERSHIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRESNAHAN, ROB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIGGANS, JENNIFER</x:t>
-  </x:si>
-  <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
   </x:si>
   <x:si>
@@ -378,9 +405,6 @@
     <x:t>GOMEZ, JIMMY</x:t>
   </x:si>
   <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
     <x:t>CISNEROS, JESSICA</x:t>
   </x:si>
   <x:si>
@@ -394,27 +418,6 @@
   </x:si>
   <x:si>
     <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOWMAN, JAMAAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERRERA, BRANDON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AHMED, JUNAID</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -485,8 +488,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G85" totalsRowShown="0">
-  <x:autoFilter ref="A1:G85"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G86" totalsRowShown="0">
+  <x:autoFilter ref="A1:G86"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -501,8 +504,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E64" totalsRowShown="0">
-  <x:autoFilter ref="A1:E64"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E65" totalsRowShown="0">
+  <x:autoFilter ref="A1:E65"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -515,8 +518,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D57" totalsRowShown="0">
-  <x:autoFilter ref="A1:D57"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D58" totalsRowShown="0">
+  <x:autoFilter ref="A1:D58"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -551,8 +554,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C48" totalsRowShown="0">
-  <x:autoFilter ref="A1:C48"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C49" totalsRowShown="0">
+  <x:autoFilter ref="A1:C49"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -850,7 +853,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G85"/>
+  <x:dimension ref="A1:G86"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -903,7 +906,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>10000</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -911,22 +914,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
+      <x:c r="E3" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F3" s="1">
-        <x:v>382</x:v>
+        <x:v>1974</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -934,183 +937,183 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>2649</x:v>
+        <x:v>1642140</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="E5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>685627</x:v>
+        <x:v>-31053</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="E6" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>214831</x:v>
+        <x:v>-46</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>4383748</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>338408</x:v>
+        <x:v>499160</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>4383749</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>3515615</x:v>
+        <x:v>663879</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>11995</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1118,22 +1121,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>382</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1141,22 +1144,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>164138</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1164,10 +1167,10 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>49</x:v>
@@ -1176,10 +1179,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>4968501</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1187,22 +1190,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>579319</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1210,22 +1213,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>3515616</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1233,22 +1236,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>715</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1256,22 +1259,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>938</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1279,22 +1282,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>825293</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1302,22 +1305,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>63298</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1325,22 +1328,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>600000</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1348,22 +1351,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>3985698</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1371,252 +1374,252 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>299290</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>3985700</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>500000</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>382</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1870</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="F28" s="1">
-        <x:v>2000000</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>-9678</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>5734013</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>20140909</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="C32" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>104048</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>60000</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1624,22 +1627,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>152765</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1653,62 +1656,62 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>198972</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>253656</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>350000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1716,91 +1719,91 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>1183678</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="1">
         <x:v>1183678</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D40" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="F40" s="1">
-        <x:v>-62727</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>382</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1808,22 +1811,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>33653</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1831,22 +1834,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>2651</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1854,68 +1857,68 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>-6917</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>149773</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>20304</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1923,22 +1926,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>253750</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1946,22 +1949,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>104555</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -1969,68 +1972,68 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>249314</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D50" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="D50" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F50" s="1">
-        <x:v>104555</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>382</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2038,22 +2041,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>382</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2061,22 +2064,22 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>58441</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2084,19 +2087,19 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F54" s="1">
         <x:v>382</x:v>
@@ -2107,42 +2110,42 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>14264</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="F56" s="1">
         <x:v>382</x:v>
@@ -2153,45 +2156,45 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>2435149</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>10517822</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2199,45 +2202,45 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>500346</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>1046779</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2245,160 +2248,160 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>1426379</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="D62" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>900000</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>159276</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>1426379</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>362844</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>333</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>382</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2406,68 +2409,68 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>3575107</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="D69" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E69" s="1" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E69" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="F69" s="1">
-        <x:v>59748</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
         <x:v>118</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>-28160</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2475,22 +2478,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E71" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E71" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="F71" s="1">
-        <x:v>39386</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2498,22 +2501,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>198972</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2521,91 +2524,91 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>4379243</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C74" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D74" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E74" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="C74" s="1" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D74" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E74" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F74" s="1">
-        <x:v>3232621</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>2326917</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="s">
         <x:v>124</x:v>
       </x:c>
-      <x:c r="C76" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>4379246</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2613,22 +2616,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>333</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2636,79 +2639,79 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1974</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>1642140</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-31053</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
         <x:v>128</x:v>
@@ -2717,56 +2720,56 @@
         <x:v>129</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>2326917</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>499160</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2774,48 +2777,71 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>663879</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D85" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E85" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F85" s="1">
+        <x:v>2326917</x:v>
+      </x:c>
+      <x:c r="G85" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:7">
+      <x:c r="A86" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="D85" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E85" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F85" s="1">
-        <x:v>663879</x:v>
-      </x:c>
-      <x:c r="G85" s="1" t="s">
-        <x:v>36</x:v>
+      <x:c r="B86" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C86" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D86" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E86" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F86" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="G86" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2834,7 +2860,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E64"/>
+  <x:dimension ref="A1:E65"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -2864,13 +2890,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2881,13 +2907,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>499160</x:v>
@@ -2904,7 +2930,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>63298</x:v>
@@ -2918,10 +2944,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>60000</x:v>
@@ -2932,13 +2958,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>825293</x:v>
@@ -2949,30 +2975,30 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>104048</x:v>
@@ -2983,30 +3009,30 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>153098</x:v>
@@ -3017,13 +3043,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>-28160</x:v>
@@ -3034,30 +3060,30 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>333</x:v>
@@ -3068,13 +3094,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3085,30 +3111,30 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>8758871</x:v>
@@ -3119,47 +3145,47 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>-9678</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>59748</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>4968501</x:v>
@@ -3170,30 +3196,30 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>7971780</x:v>
@@ -3204,47 +3230,47 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>2367356</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>2852758</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>209110</x:v>
@@ -3255,13 +3281,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>149773</x:v>
@@ -3272,13 +3298,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>9267843</x:v>
@@ -3289,47 +3315,47 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>7610550</x:v>
@@ -3340,13 +3366,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3357,30 +3383,30 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3391,13 +3417,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3408,13 +3434,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3425,13 +3451,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3445,27 +3471,27 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3476,10 +3502,10 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
         <x:v>63</x:v>
@@ -3496,7 +3522,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
         <x:v>63</x:v>
@@ -3510,30 +3536,30 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3544,13 +3570,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>938</x:v>
@@ -3561,13 +3587,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>1974</x:v>
@@ -3578,13 +3604,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>1206055</x:v>
@@ -3598,10 +3624,10 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>382</x:v>
@@ -3612,30 +3638,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>253656</x:v>
@@ -3646,30 +3672,30 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>408441</x:v>
@@ -3680,30 +3706,30 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>11995</x:v>
@@ -3714,19 +3740,19 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
@@ -3737,7 +3763,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>382</x:v>
@@ -3748,30 +3774,30 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>382</x:v>
@@ -3785,10 +3811,10 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>382</x:v>
@@ -3799,30 +3825,30 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>39386</x:v>
@@ -3833,50 +3859,50 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D59" s="1">
-        <x:v>14264</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D60" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D61" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>12</x:v>
@@ -3884,16 +3910,16 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D62" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
         <x:v>12</x:v>
@@ -3901,35 +3927,52 @@
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D63" s="1">
-        <x:v>900000</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D64" s="1">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="E64" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:5">
+      <x:c r="A65" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D65" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="E64" s="1" t="s">
+      <x:c r="E65" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -3949,7 +3992,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D57"/>
+  <x:dimension ref="A1:D58"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="5" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -3975,10 +4018,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -3989,10 +4032,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -4006,7 +4049,7 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>63298</x:v>
@@ -4017,10 +4060,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>60000</x:v>
@@ -4031,10 +4074,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>825293</x:v>
@@ -4045,24 +4088,24 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>1642140</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>104048</x:v>
@@ -4073,24 +4116,24 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>153098</x:v>
@@ -4101,10 +4144,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>-28160</x:v>
@@ -4115,24 +4158,24 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>2000000</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>333</x:v>
@@ -4143,10 +4186,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4157,24 +4200,24 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>8758871</x:v>
@@ -4185,24 +4228,24 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>50070</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>4968501</x:v>
@@ -4213,24 +4256,24 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1327758</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>7971780</x:v>
@@ -4241,24 +4284,24 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5220114</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>9626726</x:v>
@@ -4269,38 +4312,38 @@
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>7610550</x:v>
@@ -4311,10 +4354,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4325,24 +4368,24 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4353,10 +4396,10 @@
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4367,10 +4410,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4381,24 +4424,24 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4409,7 +4452,7 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
         <x:v>63</x:v>
@@ -4423,7 +4466,7 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>63</x:v>
@@ -4437,24 +4480,24 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4465,10 +4508,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>938</x:v>
@@ -4479,10 +4522,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>1208411</x:v>
@@ -4493,24 +4536,24 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>253656</x:v>
@@ -4521,24 +4564,24 @@
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>2326917</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>408441</x:v>
@@ -4549,24 +4592,24 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>338408</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>11995</x:v>
@@ -4577,16 +4620,16 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>-31053</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
@@ -4594,7 +4637,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>382</x:v>
@@ -4605,24 +4648,24 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>382</x:v>
@@ -4633,10 +4676,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>382</x:v>
@@ -4647,24 +4690,24 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>-46</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>39386</x:v>
@@ -4675,41 +4718,41 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C52" s="1">
-        <x:v>14264</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C53" s="1">
-        <x:v>164138</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C54" s="1">
-        <x:v>-62727</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
         <x:v>12</x:v>
@@ -4717,13 +4760,13 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C55" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
         <x:v>12</x:v>
@@ -4731,29 +4774,43 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C56" s="1">
-        <x:v>900000</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C57" s="1">
+        <x:v>900000</x:v>
+      </x:c>
+      <x:c r="D57" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C58" s="1">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="D57" s="1" t="s">
+      <x:c r="D58" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
     </x:row>
@@ -4795,7 +4852,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4806,18 +4863,18 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>4142140</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>1677070</x:v>
@@ -4828,7 +4885,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4839,29 +4896,29 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>6597942</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>31325878</x:v>
@@ -4872,29 +4929,29 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>7170572</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>7610550</x:v>
@@ -4905,7 +4962,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4916,18 +4973,18 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4938,7 +4995,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -4949,18 +5006,18 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -4982,18 +5039,18 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -5004,7 +5061,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>1209349</x:v>
@@ -5015,18 +5072,18 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>4653834</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>662097</x:v>
@@ -5037,18 +5094,18 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>307355</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>12377</x:v>
@@ -5059,18 +5116,18 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>249314</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>764</x:v>
@@ -5081,21 +5138,21 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14218</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="1">
-        <x:v>203524</x:v>
+        <x:v>315874</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>12</x:v>
@@ -5103,7 +5160,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>-62727</x:v>
@@ -5114,7 +5171,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>214831</x:v>
@@ -5125,18 +5182,18 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>900000</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>382</x:v>
@@ -5179,7 +5236,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5187,7 +5244,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>5819210</x:v>
@@ -5195,7 +5252,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5203,7 +5260,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5211,7 +5268,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>37923820</x:v>
@@ -5219,7 +5276,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5227,7 +5284,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>14781122</x:v>
@@ -5235,7 +5292,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5243,7 +5300,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5251,7 +5308,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5259,7 +5316,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5275,7 +5332,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5283,7 +5340,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>1209349</x:v>
@@ -5291,7 +5348,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>5315931</x:v>
@@ -5299,7 +5356,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>319732</x:v>
@@ -5307,7 +5364,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>250078</x:v>
@@ -5315,15 +5372,15 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" s="1">
-        <x:v>217742</x:v>
+        <x:v>330092</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5331,7 +5388,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5339,7 +5396,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>900382</x:v>
@@ -5361,7 +5418,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C48"/>
+  <x:dimension ref="A1:C49"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="4" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -5386,7 +5443,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5394,10 +5451,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>499160</x:v>
@@ -5405,10 +5462,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>2500666</x:v>
@@ -5419,7 +5476,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>216063</x:v>
@@ -5427,10 +5484,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>164048</x:v>
@@ -5438,10 +5495,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2439273</x:v>
@@ -5449,10 +5506,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5463,7 +5520,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5471,10 +5528,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>8758489</x:v>
@@ -5482,10 +5539,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>3904224</x:v>
@@ -5493,10 +5550,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>764</x:v>
@@ -5507,7 +5564,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>500346</x:v>
@@ -5515,10 +5572,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>19591653</x:v>
@@ -5526,10 +5583,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>149773</x:v>
@@ -5537,10 +5594,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>5018571</x:v>
@@ -5548,10 +5605,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5559,10 +5616,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>10626696</x:v>
@@ -5570,10 +5627,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>4154426</x:v>
@@ -5581,10 +5638,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5592,10 +5649,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5603,10 +5660,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5614,10 +5671,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5625,10 +5682,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5636,10 +5693,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5647,10 +5704,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5658,10 +5715,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5669,7 +5726,7 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>63</x:v>
@@ -5680,7 +5737,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>63</x:v>
@@ -5691,10 +5748,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5705,7 +5762,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5713,10 +5770,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1206055</x:v>
@@ -5724,10 +5781,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>3294</x:v>
@@ -5735,10 +5792,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>603656</x:v>
@@ -5746,10 +5803,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>58441</x:v>
@@ -5757,10 +5814,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>4653834</x:v>
@@ -5768,10 +5825,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>338408</x:v>
@@ -5779,10 +5836,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>382</x:v>
@@ -5790,10 +5847,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>11995</x:v>
@@ -5801,10 +5858,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>-31053</x:v>
@@ -5812,10 +5869,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>764</x:v>
@@ -5826,7 +5883,7 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>249314</x:v>
@@ -5834,67 +5891,78 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" s="1">
-        <x:v>178402</x:v>
+        <x:v>112350</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C44" s="1">
-        <x:v>39386</x:v>
+        <x:v>178402</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C45" s="1">
-        <x:v>-46</x:v>
+        <x:v>39386</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:3">
       <x:c r="A46" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C46" s="1">
-        <x:v>-62727</x:v>
+        <x:v>-46</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:3">
       <x:c r="A47" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C47" s="1">
-        <x:v>214831</x:v>
+        <x:v>-62727</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:3">
       <x:c r="A48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C48" s="1">
+        <x:v>214831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:3">
+      <x:c r="A49" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C49" s="1">
         <x:v>900382</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -144,40 +144,250 @@
     <x:t>RJC VICTORY FUND</x:t>
   </x:si>
   <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VON WILPERT, MARNI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COGNETTI, PAIGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRIEDMAN, JASON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOMEZ, JIMMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CISNEROS, JESSICA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POWELL, DENISE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STELSON, JANELLE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALINDO, MAUREEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SULLIVAN, MAURA CORBY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUSH, CORI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIGGANS, JENNIFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
     <x:t>GALLREIN, ED</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOLDMAN, DANIEL</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
     <x:t>GARCIA, JOHNNY</x:t>
   </x:si>
   <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRESNAHAN, ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GONZALEZ, VICENTE</x:t>
   </x:si>
   <x:si>
     <x:t>BIRD, SHANNON KATHLEEN</x:t>
@@ -186,21 +396,12 @@
     <x:t>CO</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
     <x:t>HERNANDEZ, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>BABB TOMLINSON, LAUREN</x:t>
   </x:si>
   <x:si>
@@ -210,18 +411,6 @@
     <x:t>FOUSHEE, VALERIE</x:t>
   </x:si>
   <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
     <x:t>PAULINA LUNA, ANNA</x:t>
   </x:si>
   <x:si>
@@ -229,195 +418,6 @@
   </x:si>
   <x:si>
     <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRESNAHAN, ROB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GONZALEZ, VICENTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STELSON, JANELLE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONLEY, CAIT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALINDO, MAUREEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SULLIVAN, MAURA CORBY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KIGGANS, JENNIFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIPETRI, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VON WILPERT, MARNI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COGNETTI, PAIGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRIEDMAN, JASON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOMEZ, JIMMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CISNEROS, JESSICA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>POWELL, DENISE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1113,30 +1113,30 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>3515615</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>11995</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1150,13 +1150,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F13" s="1">
         <x:v>382</x:v>
@@ -1167,25 +1167,25 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>164138</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
@@ -1196,19 +1196,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>4968501</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
@@ -1219,16 +1219,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>579319</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1236,22 +1236,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>3515616</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1259,22 +1259,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>715</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1282,22 +1282,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>938</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1305,68 +1305,68 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>825293</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>63298</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>600000</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1374,71 +1374,71 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>3985698</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>299290</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>3985700</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
@@ -1449,16 +1449,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>20</x:v>
@@ -1466,68 +1466,68 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>382</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>1870</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>2000000</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>20</x:v>
@@ -1535,45 +1535,45 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>-9678</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>5734013</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1581,68 +1581,68 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>20140909</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>104048</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>60000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1650,22 +1650,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>152765</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1673,22 +1673,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>198972</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>20</x:v>
@@ -1696,45 +1696,45 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>253656</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>350000</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1742,68 +1742,68 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>1183678</x:v>
+        <x:v>58441</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>-62727</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1817,19 +1817,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>382</x:v>
+        <x:v>14264</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
@@ -1840,16 +1840,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>33653</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1857,25 +1857,25 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>2651</x:v>
+        <x:v>2435149</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
@@ -1886,39 +1886,39 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>-6917</x:v>
+        <x:v>10517822</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>149773</x:v>
+        <x:v>500346</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1926,22 +1926,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>20304</x:v>
+        <x:v>1046779</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1949,114 +1949,114 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>253750</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>104555</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>249314</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>112350</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>104555</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2070,13 +2070,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F53" s="1">
         <x:v>382</x:v>
@@ -2093,16 +2093,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>382</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2110,22 +2110,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>58441</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2133,22 +2133,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>382</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2156,91 +2156,91 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>14264</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>382</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>2435149</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>10517822</x:v>
+        <x:v>3515615</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2248,22 +2248,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>500346</x:v>
+        <x:v>11995</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2271,22 +2271,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>1046779</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2294,68 +2294,68 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>1426379</x:v>
+        <x:v>164138</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>900000</x:v>
+        <x:v>4968501</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>159276</x:v>
+        <x:v>579319</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2363,45 +2363,45 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>1426379</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>10000</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2415,13 +2415,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F68" s="1">
         <x:v>382</x:v>
@@ -2438,16 +2438,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>2649</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -2455,22 +2455,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>685627</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2478,45 +2478,45 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>214831</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>4383748</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2524,45 +2524,45 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>338408</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>4383749</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>12</x:v>
@@ -2570,68 +2570,68 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>362844</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>333</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>382</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2639,68 +2639,68 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>3575107</x:v>
+        <x:v>104555</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>59748</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>-28160</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2708,22 +2708,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>39386</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2731,22 +2731,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>198972</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2754,22 +2754,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>4379243</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2777,45 +2777,45 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>3232621</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>2326917</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>20</x:v>
@@ -2823,22 +2823,22 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>12</x:v>
@@ -2890,13 +2890,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>253750</x:v>
@@ -2924,10 +2924,10 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>11</x:v>
@@ -2941,7 +2941,7 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>28</x:v>
@@ -2958,10 +2958,10 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>11</x:v>
@@ -3009,7 +3009,7 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>10</x:v>
@@ -3043,10 +3043,10 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>11</x:v>
@@ -3060,10 +3060,10 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>11</x:v>
@@ -3077,10 +3077,10 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>11</x:v>
@@ -3094,13 +3094,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>715</x:v>
@@ -3111,13 +3111,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>299290</x:v>
@@ -3128,10 +3128,10 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>38</x:v>
@@ -3145,10 +3145,10 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>38</x:v>
@@ -3162,10 +3162,10 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>38</x:v>
@@ -3179,10 +3179,10 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>38</x:v>
@@ -3213,7 +3213,7 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>37</x:v>
@@ -3230,10 +3230,10 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>38</x:v>
@@ -3247,10 +3247,10 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>38</x:v>
@@ -3264,10 +3264,10 @@
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>38</x:v>
@@ -3281,10 +3281,10 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>38</x:v>
@@ -3298,10 +3298,10 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>38</x:v>
@@ -3315,13 +3315,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>-6917</x:v>
@@ -3332,7 +3332,7 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>33</x:v>
@@ -3349,7 +3349,7 @@
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
         <x:v>33</x:v>
@@ -3366,13 +3366,13 @@
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>5734395</x:v>
@@ -3383,13 +3383,13 @@
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>20140909</x:v>
@@ -3400,13 +3400,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>20304</x:v>
@@ -3417,13 +3417,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>10561475</x:v>
@@ -3434,13 +3434,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>382</x:v>
@@ -3451,13 +3451,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>2649</x:v>
@@ -3468,13 +3468,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>2435149</x:v>
@@ -3485,13 +3485,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>685627</x:v>
@@ -3502,13 +3502,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>2651</x:v>
@@ -3519,13 +3519,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>600000</x:v>
@@ -3536,13 +3536,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>200842</x:v>
@@ -3553,13 +3553,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>198972</x:v>
@@ -3573,7 +3573,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
         <x:v>15</x:v>
@@ -3604,7 +3604,7 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>14</x:v>
@@ -3621,7 +3621,7 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>14</x:v>
@@ -3641,7 +3641,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
         <x:v>29</x:v>
@@ -3655,10 +3655,10 @@
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
         <x:v>29</x:v>
@@ -3689,7 +3689,7 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
         <x:v>28</x:v>
@@ -3706,10 +3706,10 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
         <x:v>23</x:v>
@@ -3723,10 +3723,10 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>23</x:v>
@@ -3757,10 +3757,10 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>23</x:v>
@@ -3774,13 +3774,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>249314</x:v>
@@ -3791,13 +3791,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>382</x:v>
@@ -3808,13 +3808,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>382</x:v>
@@ -3842,10 +3842,10 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
         <x:v>26</x:v>
@@ -3859,10 +3859,10 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>26</x:v>
@@ -3876,10 +3876,10 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
         <x:v>26</x:v>
@@ -3893,10 +3893,10 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>26</x:v>
@@ -3910,13 +3910,13 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>-62727</x:v>
@@ -3927,13 +3927,13 @@
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>214831</x:v>
@@ -3944,13 +3944,13 @@
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>900000</x:v>
@@ -3961,13 +3961,13 @@
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>382</x:v>
@@ -4018,10 +4018,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -4046,7 +4046,7 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
         <x:v>11</x:v>
@@ -4074,7 +4074,7 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>11</x:v>
@@ -4144,7 +4144,7 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
         <x:v>11</x:v>
@@ -4158,7 +4158,7 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
         <x:v>11</x:v>
@@ -4172,7 +4172,7 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>11</x:v>
@@ -4189,7 +4189,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>715</x:v>
@@ -4200,10 +4200,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>299290</x:v>
@@ -4214,7 +4214,7 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
         <x:v>38</x:v>
@@ -4228,7 +4228,7 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
         <x:v>38</x:v>
@@ -4242,7 +4242,7 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
         <x:v>38</x:v>
@@ -4284,7 +4284,7 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
         <x:v>38</x:v>
@@ -4298,7 +4298,7 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
         <x:v>38</x:v>
@@ -4315,7 +4315,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>-6917</x:v>
@@ -4354,10 +4354,10 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>5734395</x:v>
@@ -4368,10 +4368,10 @@
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>20140909</x:v>
@@ -4382,10 +4382,10 @@
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>10581779</x:v>
@@ -4399,7 +4399,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>382</x:v>
@@ -4410,10 +4410,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>2649</x:v>
@@ -4427,7 +4427,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>2435149</x:v>
@@ -4441,7 +4441,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>685627</x:v>
@@ -4452,10 +4452,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>2651</x:v>
@@ -4469,7 +4469,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>600000</x:v>
@@ -4480,10 +4480,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>200842</x:v>
@@ -4494,10 +4494,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>198972</x:v>
@@ -4508,7 +4508,7 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
         <x:v>15</x:v>
@@ -4536,7 +4536,7 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>29</x:v>
@@ -4550,7 +4550,7 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
         <x:v>29</x:v>
@@ -4592,7 +4592,7 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
         <x:v>23</x:v>
@@ -4606,7 +4606,7 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>23</x:v>
@@ -4634,7 +4634,7 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
         <x:v>23</x:v>
@@ -4651,7 +4651,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>249314</x:v>
@@ -4665,7 +4665,7 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>382</x:v>
@@ -4676,10 +4676,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B49" s="1" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>382</x:v>
@@ -4704,7 +4704,7 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
         <x:v>26</x:v>
@@ -4718,7 +4718,7 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
         <x:v>26</x:v>
@@ -4732,7 +4732,7 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
         <x:v>26</x:v>
@@ -4746,7 +4746,7 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
         <x:v>26</x:v>
@@ -4760,10 +4760,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>-62727</x:v>
@@ -4777,7 +4777,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>214831</x:v>
@@ -4788,10 +4788,10 @@
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>900000</x:v>
@@ -4802,10 +4802,10 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>382</x:v>
@@ -4852,7 +4852,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -4885,7 +4885,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>715</x:v>
@@ -4896,7 +4896,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>299290</x:v>
@@ -4929,7 +4929,7 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>-6917</x:v>
@@ -4962,7 +4962,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>5734395</x:v>
@@ -4973,7 +4973,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>20140909</x:v>
@@ -4984,7 +4984,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>10582161</x:v>
@@ -4995,7 +4995,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2649</x:v>
@@ -5006,7 +5006,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>2435149</x:v>
@@ -5017,7 +5017,7 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>685627</x:v>
@@ -5028,7 +5028,7 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>602651</x:v>
@@ -5039,7 +5039,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>200842</x:v>
@@ -5050,7 +5050,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>198972</x:v>
@@ -5116,7 +5116,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>249314</x:v>
@@ -5127,7 +5127,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>764</x:v>
@@ -5160,7 +5160,7 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>-62727</x:v>
@@ -5171,7 +5171,7 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>214831</x:v>
@@ -5182,7 +5182,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>900000</x:v>
@@ -5193,7 +5193,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>382</x:v>
@@ -5236,7 +5236,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>253750</x:v>
@@ -5252,7 +5252,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>715</x:v>
@@ -5260,7 +5260,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>299290</x:v>
@@ -5276,7 +5276,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>-6917</x:v>
@@ -5292,7 +5292,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>5734395</x:v>
@@ -5300,7 +5300,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>30723070</x:v>
@@ -5308,7 +5308,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>2649</x:v>
@@ -5316,7 +5316,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>3120776</x:v>
@@ -5324,7 +5324,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>602651</x:v>
@@ -5332,7 +5332,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>399814</x:v>
@@ -5364,7 +5364,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>250078</x:v>
@@ -5380,7 +5380,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>-62727</x:v>
@@ -5388,7 +5388,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>214831</x:v>
@@ -5396,7 +5396,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>900382</x:v>
@@ -5440,10 +5440,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>253750</x:v>
@@ -5473,7 +5473,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
         <x:v>11</x:v>
@@ -5484,7 +5484,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>11</x:v>
@@ -5509,7 +5509,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>715</x:v>
@@ -5517,10 +5517,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>299290</x:v>
@@ -5528,7 +5528,7 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
         <x:v>38</x:v>
@@ -5561,7 +5561,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>38</x:v>
@@ -5572,7 +5572,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
         <x:v>38</x:v>
@@ -5583,7 +5583,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
         <x:v>38</x:v>
@@ -5608,7 +5608,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>-6917</x:v>
@@ -5641,7 +5641,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>382</x:v>
@@ -5652,7 +5652,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>5734013</x:v>
@@ -5663,7 +5663,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>34035</x:v>
@@ -5671,10 +5671,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>20304</x:v>
@@ -5682,10 +5682,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>10000</x:v>
@@ -5696,7 +5696,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>30658731</x:v>
@@ -5707,7 +5707,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>2649</x:v>
@@ -5718,7 +5718,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>3120776</x:v>
@@ -5729,7 +5729,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>600000</x:v>
@@ -5740,7 +5740,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>2651</x:v>
@@ -5751,7 +5751,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1870</x:v>
@@ -5759,10 +5759,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B31" s="1" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>397944</x:v>
@@ -5847,7 +5847,7 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
         <x:v>23</x:v>
@@ -5872,7 +5872,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>764</x:v>
@@ -5880,10 +5880,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>249314</x:v>
@@ -5913,7 +5913,7 @@
     </x:row>
     <x:row r="45" spans="1:3">
       <x:c r="A45" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>26</x:v>
@@ -5938,7 +5938,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>-62727</x:v>
@@ -5949,7 +5949,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>214831</x:v>
@@ -5960,7 +5960,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>900382</x:v>

--- a/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
+++ b/reports/pro-israel/pro-israel-independent-expenditure-region.xlsx
@@ -138,6 +138,132 @@
     <x:t>IL</x:t>
   </x:si>
   <x:si>
+    <x:t>BIRD, SHANNON KATHLEEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BABB TOMLINSON, LAUREN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FOUSHEE, VALERIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00936724</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BROWN, SHERROD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VILLEGAS, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSS, JEREMY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAVANAUGH, JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, KINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WIENER, SCOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENNETT, REBECCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WAY, TAHESHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -153,9 +279,6 @@
     <x:t>VON WILPERT, MARNI</x:t>
   </x:si>
   <x:si>
-    <x:t>48</x:t>
-  </x:si>
-  <x:si>
     <x:t>COGNETTI, PAIGE</x:t>
   </x:si>
   <x:si>
@@ -165,42 +288,21 @@
     <x:t>FRIEDMAN, JASON</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOMEZ, JIMMY</x:t>
   </x:si>
   <x:si>
     <x:t>34</x:t>
   </x:si>
   <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>CISNEROS, JESSICA</x:t>
   </x:si>
   <x:si>
     <x:t>28</x:t>
   </x:si>
   <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>POWELL, DENISE</x:t>
   </x:si>
   <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00935049</x:t>
   </x:si>
   <x:si>
@@ -210,60 +312,99 @@
     <x:t>MILLER, DONNA</x:t>
   </x:si>
   <x:si>
-    <x:t>VILLEGAS, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOSS, JEREMY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAVANAUGH, JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAMPA-NAJJAR, AMMAR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, KINA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WIENER, SCOTT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENNETT, REBECCA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAY, TAHESHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABUGHAZALEH, KATHERINE M.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
+    <x:t>STEVENS, HALEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CRAIG, ANGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BELL, WESLEY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCADAMS, BEN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TRUMP, DONALD J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LURIA, ELAINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOSTETTLER, JOHN N</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCMORROW, MALLORY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMIWALA, BUSHRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRESNAHAN, ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GONZALEZ, VICENTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOLDMAN, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GARCIA, JOHNNY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
   </x:si>
   <x:si>
     <x:t>STELSON, JANELLE</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>CONLEY, CAIT</x:t>
   </x:si>
   <x:si>
@@ -273,151 +414,19 @@
     <x:t>GALINDO, MAUREEN</x:t>
   </x:si>
   <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
     <x:t>SULLIVAN, MAURA CORBY</x:t>
   </x:si>
   <x:si>
     <x:t>BUSH, CORI</x:t>
   </x:si>
   <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
-    <x:t>C00936724</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELECT CHICAGO WOMEN AKA ECW</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
+    <x:t>HUSTED, JON</x:t>
   </x:si>
   <x:si>
     <x:t>KIGGANS, JENNIFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00684969</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JDCA PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CRAIG, ANGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCADAMS, BEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIPETRI, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOLDMAN, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GARCIA, JOHNNY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CONYEARS-ERVIN, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TRUMP, DONALD J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LURIA, ELAINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COOPER, ROY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOSTETTLER, JOHN N</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMIWALA, BUSHRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRESNAHAN, ROB</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GONZALEZ, VICENTE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BIRD, SHANNON KATHLEEN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BABB TOMLINSON, LAUREN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FOUSHEE, VALERIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAULINA LUNA, ANNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -488,8 +497,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G86" totalsRowShown="0">
-  <x:autoFilter ref="A1:G86"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:G88" totalsRowShown="0">
+  <x:autoFilter ref="A1:G88"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -504,8 +513,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E65" totalsRowShown="0">
-  <x:autoFilter ref="A1:E65"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:E67" totalsRowShown="0">
+  <x:autoFilter ref="A1:E67"/>
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="candidate_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_district" dataDxfId="0"/>
@@ -518,8 +527,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D58" totalsRowShown="0">
-  <x:autoFilter ref="A1:D58"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:D60" totalsRowShown="0">
+  <x:autoFilter ref="A1:D60"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="candidate_office_district" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -531,8 +540,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C33" totalsRowShown="0">
-  <x:autoFilter ref="A1:C33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C35" totalsRowShown="0">
+  <x:autoFilter ref="A1:C35"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -543,8 +552,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B22" totalsRowShown="0">
-  <x:autoFilter ref="A1:B22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Table5" displayName="Table5" ref="A1:B23" totalsRowShown="0">
+  <x:autoFilter ref="A1:B23"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="candidate_office_state" dataDxfId="0"/>
     <x:tableColumn id="2" name="expenditure" dataDxfId="0"/>
@@ -554,8 +563,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C49" totalsRowShown="0">
-  <x:autoFilter ref="A1:C49"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Table6" displayName="Table6" ref="A1:C50" totalsRowShown="0">
+  <x:autoFilter ref="A1:C50"/>
   <x:tableColumns count="3">
     <x:tableColumn id="1" name="committee_name" dataDxfId="0"/>
     <x:tableColumn id="2" name="candidate_office_state" dataDxfId="0"/>
@@ -853,7 +862,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G86"/>
+  <x:dimension ref="A1:G88"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="8" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1098,25 +1107,25 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>362844</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
@@ -1127,16 +1136,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>333</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1144,22 +1153,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>382</x:v>
+        <x:v>825293</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1167,68 +1176,68 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>3575107</x:v>
+        <x:v>63298</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>59748</x:v>
+        <x:v>600000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>-28160</x:v>
+        <x:v>3985698</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1236,22 +1245,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>39386</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1259,10 +1268,10 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>57</x:v>
@@ -1274,30 +1283,30 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>198972</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>4379243</x:v>
+        <x:v>3985700</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1305,22 +1314,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>3232621</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>20</x:v>
@@ -1328,48 +1337,48 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>2326917</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
@@ -1380,16 +1389,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>500000</x:v>
+        <x:v>2000000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>20</x:v>
@@ -1397,68 +1406,68 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>382</x:v>
+        <x:v>-9678</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>1870</x:v>
+        <x:v>5734013</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>2000000</x:v>
+        <x:v>20140909</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>20</x:v>
@@ -1466,45 +1475,45 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>-9678</x:v>
+        <x:v>104048</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>5734013</x:v>
+        <x:v>60000</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1512,68 +1521,68 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>20140909</x:v>
+        <x:v>152765</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>104048</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>60000</x:v>
+        <x:v>253656</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1581,22 +1590,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>152765</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1604,22 +1613,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>198972</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>20</x:v>
@@ -1627,160 +1636,160 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>253656</x:v>
+        <x:v>1183678</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>350000</x:v>
+        <x:v>362844</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1183678</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>1183678</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>382</x:v>
+        <x:v>3575107</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>382</x:v>
+        <x:v>59748</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>58441</x:v>
+        <x:v>-28160</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1788,22 +1797,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>382</x:v>
+        <x:v>39386</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1811,45 +1820,45 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>14264</x:v>
+        <x:v>198972</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>382</x:v>
+        <x:v>4379243</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1857,22 +1866,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>2435149</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>20</x:v>
@@ -1886,39 +1895,39 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>10517822</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>500346</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1926,22 +1935,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>1046779</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1949,25 +1958,25 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1426379</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
@@ -1978,39 +1987,39 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>900000</x:v>
+        <x:v>2649</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>159276</x:v>
+        <x:v>685627</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2018,45 +2027,45 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1426379</x:v>
+        <x:v>214831</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>10000</x:v>
+        <x:v>4383748</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2064,45 +2073,45 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>382</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>2649</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2110,22 +2119,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>685627</x:v>
+        <x:v>-62727</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2133,22 +2142,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>214831</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2156,22 +2165,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>4383748</x:v>
+        <x:v>33653</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2179,68 +2188,68 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>338408</x:v>
+        <x:v>2651</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>4383749</x:v>
+        <x:v>-6917</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>3515615</x:v>
+        <x:v>149773</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2248,22 +2257,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>11995</x:v>
+        <x:v>20304</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2271,22 +2280,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>117</x:v>
       </x:c>
  